--- a/tests/Tech Team test.xlsx
+++ b/tests/Tech Team test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leahy\Downloads\projects\check_cards\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leahy\RustroverProjects\check_cards\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25E7AAF-B84E-4E7C-8B1D-10976DE0A809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4185F1-E512-4192-9D99-DF7B8A56D9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="598" activeTab="2" xr2:uid="{E07B1310-9781-4220-8CE5-1396FDD10E45}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="598" activeTab="2" xr2:uid="{E07B1310-9781-4220-8CE5-1396FDD10E45}"/>
   </bookViews>
   <sheets>
     <sheet name="LEGEND" sheetId="22" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="542">
   <si>
     <t>Flexibility</t>
   </si>
@@ -1692,6 +1692,9 @@
   </si>
   <si>
     <t>A-Sq-Forw-tk/2pk-s1-Dbl/Pos3</t>
+  </si>
+  <si>
+    <t>T9*0.5</t>
   </si>
 </sst>
 </file>
@@ -2810,70 +2813,6 @@
     <xf numFmtId="20" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2928,6 +2867,70 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4457,34 +4460,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA650C99-F61D-4A1A-B5F0-A23FFC989DB0}">
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.86328125" style="4" customWidth="1"/>
     <col min="3" max="6" width="13.6640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="4.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="4"/>
-    <col min="9" max="9" width="15.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="4.46484375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4"/>
+    <col min="9" max="9" width="15.46484375" style="4" customWidth="1"/>
     <col min="10" max="10" width="8" style="4" customWidth="1"/>
-    <col min="11" max="11" width="26.109375" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="4"/>
+    <col min="11" max="11" width="26.1328125" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="8.86328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6">
+    <row r="1" spans="1:11" ht="15">
       <c r="A1" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20.399999999999999">
+    <row r="3" spans="1:11" ht="20.25">
       <c r="D3" s="29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="13.9">
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" ht="13.9">
       <c r="A7" s="5"/>
       <c r="D7" s="7" t="s">
         <v>107</v>
@@ -4497,7 +4500,7 @@
       <c r="J7" s="8"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" ht="13.9">
       <c r="A8" s="26" t="s">
         <v>27</v>
       </c>
@@ -4516,7 +4519,7 @@
       <c r="J8" s="12"/>
       <c r="K8" s="13"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" ht="13.9">
       <c r="A9" s="14" t="s">
         <v>18</v>
       </c>
@@ -4534,7 +4537,7 @@
       <c r="J9" s="12"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" ht="13.9">
       <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
@@ -4552,7 +4555,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" ht="13.9">
       <c r="A11" s="14" t="s">
         <v>20</v>
       </c>
@@ -4570,7 +4573,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="13"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" ht="13.9">
       <c r="A12" s="14" t="s">
         <v>21</v>
       </c>
@@ -4588,7 +4591,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="13"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" ht="13.9">
       <c r="A13" s="14" t="s">
         <v>98</v>
       </c>
@@ -4606,7 +4609,7 @@
       <c r="J13" s="16"/>
       <c r="K13" s="17"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" ht="13.9">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -4614,115 +4617,115 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="109" t="s">
+    <row r="18" spans="1:11" ht="13.9">
+      <c r="A18" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="110" t="s">
+      <c r="B18" s="120"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="110"/>
-      <c r="F18" s="111"/>
-      <c r="H18" s="108" t="s">
+      <c r="E18" s="121"/>
+      <c r="F18" s="122"/>
+      <c r="H18" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="108"/>
-      <c r="J18" s="108"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
       <c r="K18" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.4">
-      <c r="A19" s="98" t="s">
+    <row r="19" spans="1:11" ht="14.25">
+      <c r="A19" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="98"/>
+      <c r="B19" s="123"/>
       <c r="C19" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="99" t="s">
+      <c r="D19" s="127" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="101"/>
-      <c r="H19" s="112" t="s">
+      <c r="E19" s="128"/>
+      <c r="F19" s="129"/>
+      <c r="H19" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="113"/>
-      <c r="J19" s="114"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="126"/>
       <c r="K19" s="72" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="98" t="s">
+      <c r="A20" s="123" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="98"/>
+      <c r="B20" s="123"/>
       <c r="C20" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="104"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="132"/>
       <c r="J20" s="10"/>
       <c r="K20" s="73"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="98" t="s">
+      <c r="A21" s="123" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="98"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="104"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="132"/>
       <c r="J21" s="10"/>
       <c r="K21" s="73"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="98"/>
+      <c r="B22" s="123"/>
       <c r="C22" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="104"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="132"/>
       <c r="J22" s="10"/>
       <c r="K22" s="73"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="98" t="s">
+      <c r="A23" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="98"/>
+      <c r="B23" s="123"/>
       <c r="C23" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="102"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="104"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="132"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="98" t="s">
+      <c r="A24" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="98"/>
+      <c r="B24" s="123"/>
       <c r="C24" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="105"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="107"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="135"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
       <c r="J24" s="10"/>
       <c r="K24" s="73"/>
     </row>
@@ -4786,12 +4789,12 @@
       <c r="J29" s="90"/>
       <c r="K29" s="90"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" ht="13.9">
       <c r="A32" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="23" t="s">
         <v>30</v>
       </c>
@@ -4812,7 +4815,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1">
-      <c r="A35" s="95" t="s">
+      <c r="A35" s="136" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="20" t="s">
@@ -4832,7 +4835,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1">
-      <c r="A36" s="96"/>
+      <c r="A36" s="137"/>
       <c r="B36" s="20" t="s">
         <v>40</v>
       </c>
@@ -4848,7 +4851,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1">
-      <c r="A37" s="95" t="s">
+      <c r="A37" s="136" t="s">
         <v>47</v>
       </c>
       <c r="B37" s="20" t="s">
@@ -4868,7 +4871,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1">
-      <c r="A38" s="96"/>
+      <c r="A38" s="137"/>
       <c r="B38" s="20" t="s">
         <v>59</v>
       </c>
@@ -4884,7 +4887,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1">
-      <c r="A39" s="95" t="s">
+      <c r="A39" s="136" t="s">
         <v>48</v>
       </c>
       <c r="B39" s="20" t="s">
@@ -4900,7 +4903,7 @@
       <c r="F39" s="80"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1">
-      <c r="A40" s="96"/>
+      <c r="A40" s="137"/>
       <c r="B40" s="20" t="s">
         <v>67</v>
       </c>
@@ -4912,7 +4915,7 @@
       <c r="F40" s="80"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1">
-      <c r="A41" s="95" t="s">
+      <c r="A41" s="136" t="s">
         <v>49</v>
       </c>
       <c r="B41" s="20" t="s">
@@ -4932,7 +4935,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1">
-      <c r="A42" s="96"/>
+      <c r="A42" s="137"/>
       <c r="B42" s="20" t="s">
         <v>51</v>
       </c>
@@ -4950,22 +4953,22 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="s6n2S37i1wq4nb9ApP80f9Pye68dc8ViXb+J8XO4p/sWQybTkL+xQzeejyuEncBSNKS/Gb8tRa5J0ro0fYbdfA==" saltValue="NY064wqlxk63j9MzWE1W7Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="16">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D19:F24"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A39:A40"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D19:F24"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4977,20 +4980,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B2E247-249A-4F11-AFE9-B73F96C9B07A}">
   <dimension ref="A1:B465"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="79" customFormat="1" ht="15.6">
+    <row r="1" spans="1:2" s="79" customFormat="1" ht="15">
       <c r="A1" s="77" t="s">
         <v>110</v>
       </c>
       <c r="B1" s="78"/>
     </row>
-    <row r="3" spans="1:2" ht="14.4">
+    <row r="3" spans="1:2" ht="14.25">
       <c r="A3" s="32" t="s">
         <v>523</v>
       </c>
@@ -4998,7 +5001,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.4">
+    <row r="4" spans="1:2" ht="14.25">
       <c r="A4" s="32" t="s">
         <v>522</v>
       </c>
@@ -5006,7 +5009,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4">
+    <row r="5" spans="1:2" ht="14.25">
       <c r="A5" s="32" t="s">
         <v>524</v>
       </c>
@@ -5014,7 +5017,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.4">
+    <row r="6" spans="1:2" ht="14.25">
       <c r="A6" s="32" t="s">
         <v>525</v>
       </c>
@@ -5022,7 +5025,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4">
+    <row r="7" spans="1:2" ht="14.25">
       <c r="A7" s="32" t="s">
         <v>526</v>
       </c>
@@ -5030,7 +5033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.4">
+    <row r="8" spans="1:2" ht="14.25">
       <c r="A8" s="32" t="s">
         <v>133</v>
       </c>
@@ -5038,7 +5041,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.4">
+    <row r="9" spans="1:2" ht="14.25">
       <c r="A9" s="32" t="s">
         <v>31</v>
       </c>
@@ -5046,7 +5049,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2" ht="14.25">
       <c r="A10" s="32" t="s">
         <v>134</v>
       </c>
@@ -5054,7 +5057,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.4">
+    <row r="11" spans="1:2" ht="14.25">
       <c r="A11" s="32" t="s">
         <v>135</v>
       </c>
@@ -5062,7 +5065,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.4">
+    <row r="12" spans="1:2" ht="14.25">
       <c r="A12" s="32" t="s">
         <v>136</v>
       </c>
@@ -5070,7 +5073,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.4">
+    <row r="13" spans="1:2" ht="14.25">
       <c r="A13" s="32" t="s">
         <v>137</v>
       </c>
@@ -5078,7 +5081,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4">
+    <row r="14" spans="1:2" ht="14.25">
       <c r="A14" s="32" t="s">
         <v>138</v>
       </c>
@@ -5086,7 +5089,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.4">
+    <row r="15" spans="1:2" ht="14.25">
       <c r="A15" s="32" t="s">
         <v>139</v>
       </c>
@@ -5094,7 +5097,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.4">
+    <row r="16" spans="1:2" ht="14.25">
       <c r="A16" s="32" t="s">
         <v>140</v>
       </c>
@@ -5102,7 +5105,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.4">
+    <row r="17" spans="1:2" ht="14.25">
       <c r="A17" s="32" t="s">
         <v>141</v>
       </c>
@@ -5110,7 +5113,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.4">
+    <row r="18" spans="1:2" ht="14.25">
       <c r="A18" s="32" t="s">
         <v>142</v>
       </c>
@@ -5118,7 +5121,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.4">
+    <row r="19" spans="1:2" ht="14.25">
       <c r="A19" s="32" t="s">
         <v>143</v>
       </c>
@@ -5126,7 +5129,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.4">
+    <row r="20" spans="1:2" ht="14.25">
       <c r="A20" s="32" t="s">
         <v>144</v>
       </c>
@@ -5134,7 +5137,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14.4">
+    <row r="21" spans="1:2" ht="14.25">
       <c r="A21" s="32" t="s">
         <v>145</v>
       </c>
@@ -5142,7 +5145,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14.4">
+    <row r="22" spans="1:2" ht="14.25">
       <c r="A22" s="32" t="s">
         <v>146</v>
       </c>
@@ -5150,7 +5153,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="14.4">
+    <row r="23" spans="1:2" ht="14.25">
       <c r="A23" s="32" t="s">
         <v>147</v>
       </c>
@@ -5158,7 +5161,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="14.4">
+    <row r="24" spans="1:2" ht="14.25">
       <c r="A24" s="32" t="s">
         <v>148</v>
       </c>
@@ -5166,7 +5169,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="14.4">
+    <row r="25" spans="1:2" ht="14.25">
       <c r="A25" s="32" t="s">
         <v>149</v>
       </c>
@@ -5174,7 +5177,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="14.4">
+    <row r="26" spans="1:2" ht="14.25">
       <c r="A26" s="32" t="s">
         <v>150</v>
       </c>
@@ -5182,7 +5185,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="14.4">
+    <row r="27" spans="1:2" ht="14.25">
       <c r="A27" s="32" t="s">
         <v>151</v>
       </c>
@@ -5190,7 +5193,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="14.4">
+    <row r="28" spans="1:2" ht="14.25">
       <c r="A28" s="32" t="s">
         <v>152</v>
       </c>
@@ -5198,7 +5201,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="14.4">
+    <row r="29" spans="1:2" ht="14.25">
       <c r="A29" s="32" t="s">
         <v>32</v>
       </c>
@@ -5206,7 +5209,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="14.4">
+    <row r="30" spans="1:2" ht="14.25">
       <c r="A30" s="32" t="s">
         <v>33</v>
       </c>
@@ -5214,7 +5217,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="14.4">
+    <row r="31" spans="1:2" ht="14.25">
       <c r="A31" s="32" t="s">
         <v>153</v>
       </c>
@@ -5222,7 +5225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="14.4">
+    <row r="32" spans="1:2" ht="14.25">
       <c r="A32" s="32" t="s">
         <v>154</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="14.4">
+    <row r="33" spans="1:2" ht="14.25">
       <c r="A33" s="33" t="s">
         <v>155</v>
       </c>
@@ -5239,7 +5242,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="14.4">
+    <row r="34" spans="1:2" ht="14.25">
       <c r="A34" s="33" t="s">
         <v>82</v>
       </c>
@@ -5248,7 +5251,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="14.4">
+    <row r="35" spans="1:2" ht="14.25">
       <c r="A35" s="33" t="s">
         <v>156</v>
       </c>
@@ -5257,7 +5260,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="14.4">
+    <row r="36" spans="1:2" ht="14.25">
       <c r="A36" s="33" t="s">
         <v>157</v>
       </c>
@@ -5266,7 +5269,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="14.4">
+    <row r="37" spans="1:2" ht="14.25">
       <c r="A37" s="33" t="s">
         <v>173</v>
       </c>
@@ -5275,7 +5278,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="14.4">
+    <row r="38" spans="1:2" ht="14.25">
       <c r="A38" s="33" t="s">
         <v>174</v>
       </c>
@@ -5284,7 +5287,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="14.4">
+    <row r="39" spans="1:2" ht="14.25">
       <c r="A39" s="33" t="s">
         <v>175</v>
       </c>
@@ -5293,7 +5296,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="14.4">
+    <row r="40" spans="1:2" ht="14.25">
       <c r="A40" s="33" t="s">
         <v>176</v>
       </c>
@@ -5302,7 +5305,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="14.4">
+    <row r="41" spans="1:2" ht="14.25">
       <c r="A41" s="33" t="s">
         <v>168</v>
       </c>
@@ -5311,7 +5314,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="14.4">
+    <row r="42" spans="1:2" ht="14.25">
       <c r="A42" s="33" t="s">
         <v>169</v>
       </c>
@@ -5320,7 +5323,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="14.4">
+    <row r="43" spans="1:2" ht="14.25">
       <c r="A43" s="33" t="s">
         <v>170</v>
       </c>
@@ -5329,7 +5332,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="14.4">
+    <row r="44" spans="1:2" ht="14.25">
       <c r="A44" s="33" t="s">
         <v>171</v>
       </c>
@@ -5338,7 +5341,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="14.4">
+    <row r="45" spans="1:2" ht="14.25">
       <c r="A45" s="33" t="s">
         <v>172</v>
       </c>
@@ -5347,7 +5350,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="14.4">
+    <row r="46" spans="1:2" ht="14.25">
       <c r="A46" s="33" t="s">
         <v>163</v>
       </c>
@@ -5356,7 +5359,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="14.4">
+    <row r="47" spans="1:2" ht="14.25">
       <c r="A47" s="33" t="s">
         <v>164</v>
       </c>
@@ -5365,7 +5368,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="14.4">
+    <row r="48" spans="1:2" ht="14.25">
       <c r="A48" s="33" t="s">
         <v>165</v>
       </c>
@@ -5374,7 +5377,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="14.4">
+    <row r="49" spans="1:2" ht="14.25">
       <c r="A49" s="33" t="s">
         <v>166</v>
       </c>
@@ -5383,7 +5386,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="14.4">
+    <row r="50" spans="1:2" ht="14.25">
       <c r="A50" s="33" t="s">
         <v>167</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="14.4">
+    <row r="51" spans="1:2" ht="14.25">
       <c r="A51" s="33" t="s">
         <v>160</v>
       </c>
@@ -5401,7 +5404,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="14.4">
+    <row r="52" spans="1:2" ht="14.25">
       <c r="A52" s="33" t="s">
         <v>162</v>
       </c>
@@ -5410,7 +5413,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="14.4">
+    <row r="53" spans="1:2" ht="14.25">
       <c r="A53" s="33" t="s">
         <v>161</v>
       </c>
@@ -5419,7 +5422,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="14.4">
+    <row r="54" spans="1:2" ht="14.25">
       <c r="A54" s="33" t="s">
         <v>83</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="14.4">
+    <row r="55" spans="1:2" ht="14.25">
       <c r="A55" s="33" t="s">
         <v>84</v>
       </c>
@@ -5437,7 +5440,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="14.4">
+    <row r="56" spans="1:2" ht="14.25">
       <c r="A56" s="33" t="s">
         <v>158</v>
       </c>
@@ -5446,7 +5449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="14.4">
+    <row r="57" spans="1:2" ht="14.25">
       <c r="A57" s="33" t="s">
         <v>159</v>
       </c>
@@ -5455,7 +5458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="14.4">
+    <row r="58" spans="1:2" ht="14.25">
       <c r="A58" s="34" t="s">
         <v>177</v>
       </c>
@@ -5464,7 +5467,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="14.4">
+    <row r="59" spans="1:2" ht="14.25">
       <c r="A59" s="34" t="s">
         <v>85</v>
       </c>
@@ -5473,7 +5476,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="14.4">
+    <row r="60" spans="1:2" ht="14.25">
       <c r="A60" s="34" t="s">
         <v>178</v>
       </c>
@@ -5482,7 +5485,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="14.4">
+    <row r="61" spans="1:2" ht="14.25">
       <c r="A61" s="34" t="s">
         <v>179</v>
       </c>
@@ -5491,7 +5494,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="14.4">
+    <row r="62" spans="1:2" ht="14.25">
       <c r="A62" s="34" t="s">
         <v>180</v>
       </c>
@@ -5500,7 +5503,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="14.4">
+    <row r="63" spans="1:2" ht="14.25">
       <c r="A63" s="34" t="s">
         <v>181</v>
       </c>
@@ -5509,7 +5512,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="14.4">
+    <row r="64" spans="1:2" ht="14.25">
       <c r="A64" s="34" t="s">
         <v>182</v>
       </c>
@@ -5518,7 +5521,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="14.4">
+    <row r="65" spans="1:2" ht="14.25">
       <c r="A65" s="34" t="s">
         <v>183</v>
       </c>
@@ -5527,7 +5530,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="14.4">
+    <row r="66" spans="1:2" ht="14.25">
       <c r="A66" s="34" t="s">
         <v>184</v>
       </c>
@@ -5536,7 +5539,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="14.4">
+    <row r="67" spans="1:2" ht="14.25">
       <c r="A67" s="34" t="s">
         <v>185</v>
       </c>
@@ -5545,7 +5548,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="14.4">
+    <row r="68" spans="1:2" ht="14.25">
       <c r="A68" s="34" t="s">
         <v>186</v>
       </c>
@@ -5554,7 +5557,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="14.4">
+    <row r="69" spans="1:2" ht="14.25">
       <c r="A69" s="34" t="s">
         <v>187</v>
       </c>
@@ -5563,7 +5566,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="14.4">
+    <row r="70" spans="1:2" ht="14.25">
       <c r="A70" s="34" t="s">
         <v>188</v>
       </c>
@@ -5572,7 +5575,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="14.4">
+    <row r="71" spans="1:2" ht="14.25">
       <c r="A71" s="34" t="s">
         <v>189</v>
       </c>
@@ -5581,7 +5584,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="14.4">
+    <row r="72" spans="1:2" ht="14.25">
       <c r="A72" s="34" t="s">
         <v>190</v>
       </c>
@@ -5590,7 +5593,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="14.4">
+    <row r="73" spans="1:2" ht="14.25">
       <c r="A73" s="34" t="s">
         <v>191</v>
       </c>
@@ -5599,7 +5602,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="14.4">
+    <row r="74" spans="1:2" ht="14.25">
       <c r="A74" s="34" t="s">
         <v>192</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="14.4">
+    <row r="75" spans="1:2" ht="14.25">
       <c r="A75" s="34" t="s">
         <v>193</v>
       </c>
@@ -5617,7 +5620,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="14.4">
+    <row r="76" spans="1:2" ht="14.25">
       <c r="A76" s="34" t="s">
         <v>194</v>
       </c>
@@ -5626,7 +5629,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="14.4">
+    <row r="77" spans="1:2" ht="14.25">
       <c r="A77" s="34" t="s">
         <v>195</v>
       </c>
@@ -5635,7 +5638,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="14.4">
+    <row r="78" spans="1:2" ht="14.25">
       <c r="A78" s="34" t="s">
         <v>196</v>
       </c>
@@ -5644,7 +5647,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="14.4">
+    <row r="79" spans="1:2" ht="14.25">
       <c r="A79" s="34" t="s">
         <v>86</v>
       </c>
@@ -5653,7 +5656,7 @@
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="14.4">
+    <row r="80" spans="1:2" ht="14.25">
       <c r="A80" s="34" t="s">
         <v>87</v>
       </c>
@@ -5662,7 +5665,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="14.4">
+    <row r="81" spans="1:2" ht="14.25">
       <c r="A81" s="34" t="s">
         <v>197</v>
       </c>
@@ -5671,7 +5674,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="14.4">
+    <row r="82" spans="1:2" ht="14.25">
       <c r="A82" s="34" t="s">
         <v>198</v>
       </c>
@@ -5680,7 +5683,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="14.4">
+    <row r="83" spans="1:2" ht="14.25">
       <c r="A83" s="32" t="s">
         <v>201</v>
       </c>
@@ -5688,7 +5691,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="14.4">
+    <row r="84" spans="1:2" ht="14.25">
       <c r="A84" s="32" t="s">
         <v>202</v>
       </c>
@@ -5696,7 +5699,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="14.4">
+    <row r="85" spans="1:2" ht="14.25">
       <c r="A85" s="32" t="s">
         <v>203</v>
       </c>
@@ -5704,7 +5707,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="14.4">
+    <row r="86" spans="1:2" ht="14.25">
       <c r="A86" s="32" t="s">
         <v>204</v>
       </c>
@@ -5712,7 +5715,7 @@
         <v>1.1500000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="14.4">
+    <row r="87" spans="1:2" ht="14.25">
       <c r="A87" s="32" t="s">
         <v>205</v>
       </c>
@@ -5720,7 +5723,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="14.4">
+    <row r="88" spans="1:2" ht="14.25">
       <c r="A88" s="32" t="s">
         <v>206</v>
       </c>
@@ -5728,7 +5731,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="14.4">
+    <row r="89" spans="1:2" ht="14.25">
       <c r="A89" s="32" t="s">
         <v>207</v>
       </c>
@@ -5736,7 +5739,7 @@
         <v>2.3499999999999996</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="14.4">
+    <row r="90" spans="1:2" ht="14.25">
       <c r="A90" s="32" t="s">
         <v>208</v>
       </c>
@@ -5744,7 +5747,7 @@
         <v>2.7499999999999996</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="14.4">
+    <row r="91" spans="1:2" ht="14.25">
       <c r="A91" s="32" t="s">
         <v>209</v>
       </c>
@@ -5752,7 +5755,7 @@
         <v>3.1499999999999995</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="14.4">
+    <row r="92" spans="1:2" ht="14.25">
       <c r="A92" s="32" t="s">
         <v>210</v>
       </c>
@@ -5760,7 +5763,7 @@
         <v>3.5499999999999994</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="14.4">
+    <row r="93" spans="1:2" ht="14.25">
       <c r="A93" s="32" t="s">
         <v>211</v>
       </c>
@@ -5768,7 +5771,7 @@
         <v>3.9499999999999993</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="14.4">
+    <row r="94" spans="1:2" ht="14.25">
       <c r="A94" s="32" t="s">
         <v>212</v>
       </c>
@@ -5776,7 +5779,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="14.4">
+    <row r="95" spans="1:2" ht="14.25">
       <c r="A95" s="32" t="s">
         <v>213</v>
       </c>
@@ -5784,7 +5787,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="14.4">
+    <row r="96" spans="1:2" ht="14.25">
       <c r="A96" s="32" t="s">
         <v>214</v>
       </c>
@@ -5792,7 +5795,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="14.4">
+    <row r="97" spans="1:2" ht="14.25">
       <c r="A97" s="32" t="s">
         <v>215</v>
       </c>
@@ -5800,7 +5803,7 @@
         <v>2.3999999999999995</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="14.4">
+    <row r="98" spans="1:2" ht="14.25">
       <c r="A98" s="32" t="s">
         <v>216</v>
       </c>
@@ -5808,7 +5811,7 @@
         <v>3.1999999999999993</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="14.4">
+    <row r="99" spans="1:2" ht="14.25">
       <c r="A99" s="32" t="s">
         <v>217</v>
       </c>
@@ -5816,7 +5819,7 @@
         <v>3.9999999999999991</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="14.4">
+    <row r="100" spans="1:2" ht="14.25">
       <c r="A100" s="32" t="s">
         <v>218</v>
       </c>
@@ -5824,7 +5827,7 @@
         <v>4.799999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="14.4">
+    <row r="101" spans="1:2" ht="14.25">
       <c r="A101" s="32" t="s">
         <v>219</v>
       </c>
@@ -5832,7 +5835,7 @@
         <v>0.39999999999999997</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="14.4">
+    <row r="102" spans="1:2" ht="14.25">
       <c r="A102" s="32" t="s">
         <v>220</v>
       </c>
@@ -5840,7 +5843,7 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="14.4">
+    <row r="103" spans="1:2" ht="14.25">
       <c r="A103" s="32" t="s">
         <v>221</v>
       </c>
@@ -5848,7 +5851,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="14.4">
+    <row r="104" spans="1:2" ht="14.25">
       <c r="A104" s="32" t="s">
         <v>222</v>
       </c>
@@ -5856,7 +5859,7 @@
         <v>2.4499999999999993</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="14.4">
+    <row r="105" spans="1:2" ht="14.25">
       <c r="A105" s="32" t="s">
         <v>223</v>
       </c>
@@ -5864,7 +5867,7 @@
         <v>3.2499999999999991</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="14.4">
+    <row r="106" spans="1:2" ht="14.25">
       <c r="A106" s="32" t="s">
         <v>224</v>
       </c>
@@ -5872,7 +5875,7 @@
         <v>4.0499999999999989</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="14.4">
+    <row r="107" spans="1:2" ht="14.25">
       <c r="A107" s="32" t="s">
         <v>225</v>
       </c>
@@ -5880,7 +5883,7 @@
         <v>4.8499999999999979</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="14.4">
+    <row r="108" spans="1:2" ht="14.25">
       <c r="A108" s="33" t="s">
         <v>226</v>
       </c>
@@ -5889,7 +5892,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="14.4">
+    <row r="109" spans="1:2" ht="14.25">
       <c r="A109" s="33" t="s">
         <v>227</v>
       </c>
@@ -5898,7 +5901,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="14.4">
+    <row r="110" spans="1:2" ht="14.25">
       <c r="A110" s="33" t="s">
         <v>228</v>
       </c>
@@ -5907,7 +5910,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="14.4">
+    <row r="111" spans="1:2" ht="14.25">
       <c r="A111" s="33" t="s">
         <v>229</v>
       </c>
@@ -5916,7 +5919,7 @@
         <v>0.57500000000000007</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="14.4">
+    <row r="112" spans="1:2" ht="14.25">
       <c r="A112" s="33" t="s">
         <v>230</v>
       </c>
@@ -5925,7 +5928,7 @@
         <v>0.77500000000000002</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="14.4">
+    <row r="113" spans="1:2" ht="14.25">
       <c r="A113" s="33" t="s">
         <v>231</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="14.4">
+    <row r="114" spans="1:2" ht="14.25">
       <c r="A114" s="33" t="s">
         <v>232</v>
       </c>
@@ -5943,7 +5946,7 @@
         <v>1.1749999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="14.4">
+    <row r="115" spans="1:2" ht="14.25">
       <c r="A115" s="33" t="s">
         <v>233</v>
       </c>
@@ -5952,7 +5955,7 @@
         <v>1.3749999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="14.4">
+    <row r="116" spans="1:2" ht="14.25">
       <c r="A116" s="33" t="s">
         <v>234</v>
       </c>
@@ -5961,7 +5964,7 @@
         <v>1.5749999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="14.4">
+    <row r="117" spans="1:2" ht="14.25">
       <c r="A117" s="33" t="s">
         <v>235</v>
       </c>
@@ -5970,7 +5973,7 @@
         <v>1.7749999999999997</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="14.4">
+    <row r="118" spans="1:2" ht="14.25">
       <c r="A118" s="33" t="s">
         <v>236</v>
       </c>
@@ -5979,7 +5982,7 @@
         <v>1.9749999999999996</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="14.4">
+    <row r="119" spans="1:2" ht="14.25">
       <c r="A119" s="33" t="s">
         <v>237</v>
       </c>
@@ -5988,7 +5991,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="14.4">
+    <row r="120" spans="1:2" ht="14.25">
       <c r="A120" s="33" t="s">
         <v>238</v>
       </c>
@@ -5997,7 +6000,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="14.4">
+    <row r="121" spans="1:2" ht="14.25">
       <c r="A121" s="33" t="s">
         <v>239</v>
       </c>
@@ -6006,7 +6009,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="14.4">
+    <row r="122" spans="1:2" ht="14.25">
       <c r="A122" s="33" t="s">
         <v>240</v>
       </c>
@@ -6015,7 +6018,7 @@
         <v>1.1999999999999997</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="14.4">
+    <row r="123" spans="1:2" ht="14.25">
       <c r="A123" s="33" t="s">
         <v>241</v>
       </c>
@@ -6024,7 +6027,7 @@
         <v>1.5999999999999996</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="14.4">
+    <row r="124" spans="1:2" ht="14.25">
       <c r="A124" s="33" t="s">
         <v>242</v>
       </c>
@@ -6033,7 +6036,7 @@
         <v>1.9999999999999996</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="14.4">
+    <row r="125" spans="1:2" ht="14.25">
       <c r="A125" s="33" t="s">
         <v>243</v>
       </c>
@@ -6042,7 +6045,7 @@
         <v>2.399999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="14.4">
+    <row r="126" spans="1:2" ht="14.25">
       <c r="A126" s="33" t="s">
         <v>244</v>
       </c>
@@ -6051,7 +6054,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="14.4">
+    <row r="127" spans="1:2" ht="14.25">
       <c r="A127" s="33" t="s">
         <v>245</v>
       </c>
@@ -6060,7 +6063,7 @@
         <v>0.42500000000000004</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="14.4">
+    <row r="128" spans="1:2" ht="14.25">
       <c r="A128" s="33" t="s">
         <v>246</v>
       </c>
@@ -6069,7 +6072,7 @@
         <v>0.82500000000000007</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="14.4">
+    <row r="129" spans="1:2" ht="14.25">
       <c r="A129" s="33" t="s">
         <v>247</v>
       </c>
@@ -6078,7 +6081,7 @@
         <v>1.2249999999999996</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="14.4">
+    <row r="130" spans="1:2" ht="14.25">
       <c r="A130" s="33" t="s">
         <v>248</v>
       </c>
@@ -6087,7 +6090,7 @@
         <v>1.6249999999999996</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="14.4">
+    <row r="131" spans="1:2" ht="14.25">
       <c r="A131" s="33" t="s">
         <v>249</v>
       </c>
@@ -6096,7 +6099,7 @@
         <v>2.0249999999999995</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="14.4">
+    <row r="132" spans="1:2" ht="14.25">
       <c r="A132" s="33" t="s">
         <v>250</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>2.4249999999999989</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="14.4">
+    <row r="133" spans="1:2" ht="14.25">
       <c r="A133" s="34" t="s">
         <v>251</v>
       </c>
@@ -6114,7 +6117,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="14.4">
+    <row r="134" spans="1:2" ht="14.25">
       <c r="A134" s="34" t="s">
         <v>252</v>
       </c>
@@ -6123,7 +6126,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="14.4">
+    <row r="135" spans="1:2" ht="14.25">
       <c r="A135" s="34" t="s">
         <v>253</v>
       </c>
@@ -6132,7 +6135,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="14.4">
+    <row r="136" spans="1:2" ht="14.25">
       <c r="A136" s="34" t="s">
         <v>254</v>
       </c>
@@ -6141,7 +6144,7 @@
         <v>0.34500000000000003</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="14.4">
+    <row r="137" spans="1:2" ht="14.25">
       <c r="A137" s="34" t="s">
         <v>255</v>
       </c>
@@ -6150,7 +6153,7 @@
         <v>0.46499999999999997</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="14.4">
+    <row r="138" spans="1:2" ht="14.25">
       <c r="A138" s="34" t="s">
         <v>256</v>
       </c>
@@ -6159,7 +6162,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="14.4">
+    <row r="139" spans="1:2" ht="14.25">
       <c r="A139" s="34" t="s">
         <v>257</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>0.70499999999999985</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="14.4">
+    <row r="140" spans="1:2" ht="14.25">
       <c r="A140" s="34" t="s">
         <v>258</v>
       </c>
@@ -6177,7 +6180,7 @@
         <v>0.82499999999999984</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="14.4">
+    <row r="141" spans="1:2" ht="14.25">
       <c r="A141" s="34" t="s">
         <v>259</v>
       </c>
@@ -6186,7 +6189,7 @@
         <v>0.94499999999999984</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="14.4">
+    <row r="142" spans="1:2" ht="14.25">
       <c r="A142" s="34" t="s">
         <v>260</v>
       </c>
@@ -6195,7 +6198,7 @@
         <v>1.0649999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="14.4">
+    <row r="143" spans="1:2" ht="14.25">
       <c r="A143" s="34" t="s">
         <v>261</v>
       </c>
@@ -6204,7 +6207,7 @@
         <v>1.1849999999999998</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="14.4">
+    <row r="144" spans="1:2" ht="14.25">
       <c r="A144" s="34" t="s">
         <v>262</v>
       </c>
@@ -6213,7 +6216,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="14.4">
+    <row r="145" spans="1:2" ht="14.25">
       <c r="A145" s="34" t="s">
         <v>263</v>
       </c>
@@ -6222,7 +6225,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="14.4">
+    <row r="146" spans="1:2" ht="14.25">
       <c r="A146" s="34" t="s">
         <v>264</v>
       </c>
@@ -6231,7 +6234,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="14.4">
+    <row r="147" spans="1:2" ht="14.25">
       <c r="A147" s="34" t="s">
         <v>265</v>
       </c>
@@ -6240,7 +6243,7 @@
         <v>0.71999999999999986</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="14.4">
+    <row r="148" spans="1:2" ht="14.25">
       <c r="A148" s="34" t="s">
         <v>266</v>
       </c>
@@ -6249,7 +6252,7 @@
         <v>0.95999999999999974</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="14.4">
+    <row r="149" spans="1:2" ht="14.25">
       <c r="A149" s="34" t="s">
         <v>267</v>
       </c>
@@ -6258,7 +6261,7 @@
         <v>1.1999999999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="14.4">
+    <row r="150" spans="1:2" ht="14.25">
       <c r="A150" s="34" t="s">
         <v>268</v>
       </c>
@@ -6267,7 +6270,7 @@
         <v>1.4399999999999993</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="14.4">
+    <row r="151" spans="1:2" ht="14.25">
       <c r="A151" s="34" t="s">
         <v>269</v>
       </c>
@@ -6276,7 +6279,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="14.4">
+    <row r="152" spans="1:2" ht="14.25">
       <c r="A152" s="34" t="s">
         <v>270</v>
       </c>
@@ -6285,7 +6288,7 @@
         <v>0.255</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="14.4">
+    <row r="153" spans="1:2" ht="14.25">
       <c r="A153" s="34" t="s">
         <v>271</v>
       </c>
@@ -6294,7 +6297,7 @@
         <v>0.495</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="14.4">
+    <row r="154" spans="1:2" ht="14.25">
       <c r="A154" s="34" t="s">
         <v>272</v>
       </c>
@@ -6303,7 +6306,7 @@
         <v>0.73499999999999976</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="14.4">
+    <row r="155" spans="1:2" ht="14.25">
       <c r="A155" s="34" t="s">
         <v>273</v>
       </c>
@@ -6312,7 +6315,7 @@
         <v>0.97499999999999964</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="14.4">
+    <row r="156" spans="1:2" ht="14.25">
       <c r="A156" s="34" t="s">
         <v>274</v>
       </c>
@@ -6321,7 +6324,7 @@
         <v>1.2149999999999996</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="14.4">
+    <row r="157" spans="1:2" ht="14.25">
       <c r="A157" s="34" t="s">
         <v>275</v>
       </c>
@@ -6330,7 +6333,7 @@
         <v>1.4549999999999994</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="14.4">
+    <row r="158" spans="1:2" ht="14.25">
       <c r="A158" s="32" t="s">
         <v>276</v>
       </c>
@@ -6338,7 +6341,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="14.4">
+    <row r="159" spans="1:2" ht="14.25">
       <c r="A159" s="32" t="s">
         <v>5</v>
       </c>
@@ -6346,7 +6349,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="14.4">
+    <row r="160" spans="1:2" ht="14.25">
       <c r="A160" s="32" t="s">
         <v>34</v>
       </c>
@@ -6354,7 +6357,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="14.4">
+    <row r="161" spans="1:2" ht="14.25">
       <c r="A161" s="32" t="s">
         <v>35</v>
       </c>
@@ -6362,7 +6365,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="14.4">
+    <row r="162" spans="1:2" ht="14.25">
       <c r="A162" s="32" t="s">
         <v>8</v>
       </c>
@@ -6370,7 +6373,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="14.4">
+    <row r="163" spans="1:2" ht="14.25">
       <c r="A163" s="33" t="s">
         <v>277</v>
       </c>
@@ -6379,7 +6382,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="14.4">
+    <row r="164" spans="1:2" ht="14.25">
       <c r="A164" s="33" t="s">
         <v>88</v>
       </c>
@@ -6388,7 +6391,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="14.4">
+    <row r="165" spans="1:2" ht="14.25">
       <c r="A165" s="33" t="s">
         <v>89</v>
       </c>
@@ -6397,7 +6400,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="14.4">
+    <row r="166" spans="1:2" ht="14.25">
       <c r="A166" s="33" t="s">
         <v>90</v>
       </c>
@@ -6406,7 +6409,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="14.4">
+    <row r="167" spans="1:2" ht="14.25">
       <c r="A167" s="33" t="s">
         <v>91</v>
       </c>
@@ -6415,7 +6418,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="14.4">
+    <row r="168" spans="1:2" ht="14.25">
       <c r="A168" s="34" t="s">
         <v>278</v>
       </c>
@@ -6424,7 +6427,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="14.4">
+    <row r="169" spans="1:2" ht="14.25">
       <c r="A169" s="34" t="s">
         <v>92</v>
       </c>
@@ -6433,7 +6436,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="14.4">
+    <row r="170" spans="1:2" ht="14.25">
       <c r="A170" s="34" t="s">
         <v>93</v>
       </c>
@@ -6442,7 +6445,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="14.4">
+    <row r="171" spans="1:2" ht="14.25">
       <c r="A171" s="34" t="s">
         <v>94</v>
       </c>
@@ -6451,7 +6454,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="14.4">
+    <row r="172" spans="1:2" ht="14.25">
       <c r="A172" s="34" t="s">
         <v>95</v>
       </c>
@@ -6460,7 +6463,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="14.4">
+    <row r="173" spans="1:2" ht="14.25">
       <c r="A173" s="32" t="s">
         <v>279</v>
       </c>
@@ -6468,7 +6471,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="14.4">
+    <row r="174" spans="1:2" ht="14.25">
       <c r="A174" s="32" t="s">
         <v>280</v>
       </c>
@@ -6476,7 +6479,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="14.4">
+    <row r="175" spans="1:2" ht="14.25">
       <c r="A175" s="32" t="s">
         <v>281</v>
       </c>
@@ -6484,7 +6487,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="14.4">
+    <row r="176" spans="1:2" ht="14.25">
       <c r="A176" s="32" t="s">
         <v>282</v>
       </c>
@@ -6492,7 +6495,7 @@
         <v>1.1500000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="14.4">
+    <row r="177" spans="1:2" ht="14.25">
       <c r="A177" s="32" t="s">
         <v>283</v>
       </c>
@@ -6500,7 +6503,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="14.4">
+    <row r="178" spans="1:2" ht="14.25">
       <c r="A178" s="32" t="s">
         <v>284</v>
       </c>
@@ -6508,7 +6511,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="14.4">
+    <row r="179" spans="1:2" ht="14.25">
       <c r="A179" s="32" t="s">
         <v>285</v>
       </c>
@@ -6516,7 +6519,7 @@
         <v>2.3499999999999996</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="14.4">
+    <row r="180" spans="1:2" ht="14.25">
       <c r="A180" s="33" t="s">
         <v>286</v>
       </c>
@@ -6525,7 +6528,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="14.4">
+    <row r="181" spans="1:2" ht="14.25">
       <c r="A181" s="33" t="s">
         <v>287</v>
       </c>
@@ -6534,7 +6537,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="14.4">
+    <row r="182" spans="1:2" ht="14.25">
       <c r="A182" s="33" t="s">
         <v>288</v>
       </c>
@@ -6543,7 +6546,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="14.4">
+    <row r="183" spans="1:2" ht="14.25">
       <c r="A183" s="33" t="s">
         <v>289</v>
       </c>
@@ -6552,7 +6555,7 @@
         <v>0.57500000000000007</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="14.4">
+    <row r="184" spans="1:2" ht="14.25">
       <c r="A184" s="33" t="s">
         <v>290</v>
       </c>
@@ -6561,7 +6564,7 @@
         <v>0.77500000000000002</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="14.4">
+    <row r="185" spans="1:2" ht="14.25">
       <c r="A185" s="33" t="s">
         <v>291</v>
       </c>
@@ -6570,7 +6573,7 @@
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="14.4">
+    <row r="186" spans="1:2" ht="14.25">
       <c r="A186" s="33" t="s">
         <v>292</v>
       </c>
@@ -6579,7 +6582,7 @@
         <v>1.1749999999999998</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="14.4">
+    <row r="187" spans="1:2" ht="14.25">
       <c r="A187" s="34" t="s">
         <v>293</v>
       </c>
@@ -6588,7 +6591,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="14.4">
+    <row r="188" spans="1:2" ht="14.25">
       <c r="A188" s="34" t="s">
         <v>294</v>
       </c>
@@ -6597,7 +6600,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="14.4">
+    <row r="189" spans="1:2" ht="14.25">
       <c r="A189" s="34" t="s">
         <v>295</v>
       </c>
@@ -6606,7 +6609,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="14.4">
+    <row r="190" spans="1:2" ht="14.25">
       <c r="A190" s="34" t="s">
         <v>296</v>
       </c>
@@ -6615,7 +6618,7 @@
         <v>0.34500000000000003</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="14.4">
+    <row r="191" spans="1:2" ht="14.25">
       <c r="A191" s="34" t="s">
         <v>297</v>
       </c>
@@ -6624,7 +6627,7 @@
         <v>0.46499999999999997</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="14.4">
+    <row r="192" spans="1:2" ht="14.25">
       <c r="A192" s="34" t="s">
         <v>298</v>
       </c>
@@ -6633,7 +6636,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="14.4">
+    <row r="193" spans="1:2" ht="14.25">
       <c r="A193" s="34" t="s">
         <v>299</v>
       </c>
@@ -6642,7 +6645,7 @@
         <v>0.70499999999999985</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="14.4">
+    <row r="194" spans="1:2" ht="14.25">
       <c r="A194" s="32" t="s">
         <v>300</v>
       </c>
@@ -6650,7 +6653,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="14.4">
+    <row r="195" spans="1:2" ht="14.25">
       <c r="A195" s="32" t="s">
         <v>301</v>
       </c>
@@ -6658,7 +6661,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="14.4">
+    <row r="196" spans="1:2" ht="14.25">
       <c r="A196" s="32" t="s">
         <v>302</v>
       </c>
@@ -6666,7 +6669,7 @@
         <v>0.95000000000000007</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="14.4">
+    <row r="197" spans="1:2" ht="14.25">
       <c r="A197" s="32" t="s">
         <v>303</v>
       </c>
@@ -6674,7 +6677,7 @@
         <v>1.4500000000000002</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="14.4">
+    <row r="198" spans="1:2" ht="14.25">
       <c r="A198" s="32" t="s">
         <v>304</v>
       </c>
@@ -6682,7 +6685,7 @@
         <v>1.9500000000000002</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="14.4">
+    <row r="199" spans="1:2" ht="14.25">
       <c r="A199" s="32" t="s">
         <v>305</v>
       </c>
@@ -6690,7 +6693,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="14.4">
+    <row r="200" spans="1:2" ht="14.25">
       <c r="A200" s="32" t="s">
         <v>306</v>
       </c>
@@ -6698,7 +6701,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="14.4">
+    <row r="201" spans="1:2" ht="14.25">
       <c r="A201" s="32" t="s">
         <v>307</v>
       </c>
@@ -6706,7 +6709,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="14.4">
+    <row r="202" spans="1:2" ht="14.25">
       <c r="A202" s="32" t="s">
         <v>308</v>
       </c>
@@ -6714,7 +6717,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="14.4">
+    <row r="203" spans="1:2" ht="14.25">
       <c r="A203" s="32" t="s">
         <v>309</v>
       </c>
@@ -6722,7 +6725,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="14.4">
+    <row r="204" spans="1:2" ht="14.25">
       <c r="A204" s="32" t="s">
         <v>310</v>
       </c>
@@ -6730,7 +6733,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="14.4">
+    <row r="205" spans="1:2" ht="14.25">
       <c r="A205" s="33" t="s">
         <v>311</v>
       </c>
@@ -6739,7 +6742,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="14.4">
+    <row r="206" spans="1:2" ht="14.25">
       <c r="A206" s="33" t="s">
         <v>312</v>
       </c>
@@ -6748,7 +6751,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="14.4">
+    <row r="207" spans="1:2" ht="14.25">
       <c r="A207" s="33" t="s">
         <v>313</v>
       </c>
@@ -6757,7 +6760,7 @@
         <v>0.47500000000000003</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="14.4">
+    <row r="208" spans="1:2" ht="14.25">
       <c r="A208" s="33" t="s">
         <v>314</v>
       </c>
@@ -6766,7 +6769,7 @@
         <v>0.72500000000000009</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="14.4">
+    <row r="209" spans="1:2" ht="14.25">
       <c r="A209" s="33" t="s">
         <v>315</v>
       </c>
@@ -6775,7 +6778,7 @@
         <v>0.97500000000000009</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="14.4">
+    <row r="210" spans="1:2" ht="14.25">
       <c r="A210" s="33" t="s">
         <v>316</v>
       </c>
@@ -6784,7 +6787,7 @@
         <v>1.2250000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="14.4">
+    <row r="211" spans="1:2" ht="14.25">
       <c r="A211" s="33" t="s">
         <v>317</v>
       </c>
@@ -6793,7 +6796,7 @@
         <v>1.4750000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="14.4">
+    <row r="212" spans="1:2" ht="14.25">
       <c r="A212" s="33" t="s">
         <v>318</v>
       </c>
@@ -6802,7 +6805,7 @@
         <v>1.7250000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="14.4">
+    <row r="213" spans="1:2" ht="14.25">
       <c r="A213" s="33" t="s">
         <v>319</v>
       </c>
@@ -6811,7 +6814,7 @@
         <v>1.9750000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="14.4">
+    <row r="214" spans="1:2" ht="14.25">
       <c r="A214" s="33" t="s">
         <v>320</v>
       </c>
@@ -6820,7 +6823,7 @@
         <v>2.2250000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="14.4">
+    <row r="215" spans="1:2" ht="14.25">
       <c r="A215" s="33" t="s">
         <v>321</v>
       </c>
@@ -6829,7 +6832,7 @@
         <v>2.4750000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="14.4">
+    <row r="216" spans="1:2" ht="14.25">
       <c r="A216" s="34" t="s">
         <v>322</v>
       </c>
@@ -6838,7 +6841,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="14.4">
+    <row r="217" spans="1:2" ht="14.25">
       <c r="A217" s="34" t="s">
         <v>323</v>
       </c>
@@ -6847,7 +6850,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="14.4">
+    <row r="218" spans="1:2" ht="14.25">
       <c r="A218" s="34" t="s">
         <v>324</v>
       </c>
@@ -6856,7 +6859,7 @@
         <v>0.28500000000000003</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="14.4">
+    <row r="219" spans="1:2" ht="14.25">
       <c r="A219" s="34" t="s">
         <v>325</v>
       </c>
@@ -6865,7 +6868,7 @@
         <v>0.43500000000000005</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="14.4">
+    <row r="220" spans="1:2" ht="14.25">
       <c r="A220" s="34" t="s">
         <v>326</v>
       </c>
@@ -6874,7 +6877,7 @@
         <v>0.58500000000000008</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="14.4">
+    <row r="221" spans="1:2" ht="14.25">
       <c r="A221" s="34" t="s">
         <v>327</v>
       </c>
@@ -6883,7 +6886,7 @@
         <v>0.73499999999999999</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="14.4">
+    <row r="222" spans="1:2" ht="14.25">
       <c r="A222" s="34" t="s">
         <v>328</v>
       </c>
@@ -6892,7 +6895,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="14.4">
+    <row r="223" spans="1:2" ht="14.25">
       <c r="A223" s="34" t="s">
         <v>329</v>
       </c>
@@ -6901,7 +6904,7 @@
         <v>1.0349999999999999</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="14.4">
+    <row r="224" spans="1:2" ht="14.25">
       <c r="A224" s="34" t="s">
         <v>330</v>
       </c>
@@ -6910,7 +6913,7 @@
         <v>1.1850000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="14.4">
+    <row r="225" spans="1:2" ht="14.25">
       <c r="A225" s="34" t="s">
         <v>331</v>
       </c>
@@ -6919,7 +6922,7 @@
         <v>1.335</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="14.4">
+    <row r="226" spans="1:2" ht="14.25">
       <c r="A226" s="34" t="s">
         <v>332</v>
       </c>
@@ -6928,7 +6931,7 @@
         <v>1.4850000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="14.4">
+    <row r="227" spans="1:2" ht="14.25">
       <c r="A227" s="32" t="s">
         <v>333</v>
       </c>
@@ -6936,7 +6939,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="14.4">
+    <row r="228" spans="1:2" ht="14.25">
       <c r="A228" s="32" t="s">
         <v>334</v>
       </c>
@@ -6944,7 +6947,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="14.4">
+    <row r="229" spans="1:2" ht="14.25">
       <c r="A229" s="32" t="s">
         <v>335</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="14.4">
+    <row r="230" spans="1:2" ht="14.25">
       <c r="A230" s="32" t="s">
         <v>336</v>
       </c>
@@ -6960,7 +6963,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="14.4">
+    <row r="231" spans="1:2" ht="14.25">
       <c r="A231" s="33" t="s">
         <v>337</v>
       </c>
@@ -6969,7 +6972,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="14.4">
+    <row r="232" spans="1:2" ht="14.25">
       <c r="A232" s="33" t="s">
         <v>338</v>
       </c>
@@ -6978,7 +6981,7 @@
         <v>0.52500000000000002</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="14.4">
+    <row r="233" spans="1:2" ht="14.25">
       <c r="A233" s="33" t="s">
         <v>339</v>
       </c>
@@ -6987,7 +6990,7 @@
         <v>1.075</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="14.4">
+    <row r="234" spans="1:2" ht="14.25">
       <c r="A234" s="33" t="s">
         <v>340</v>
       </c>
@@ -6996,7 +6999,7 @@
         <v>1.675</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="14.4">
+    <row r="235" spans="1:2" ht="14.25">
       <c r="A235" s="34" t="s">
         <v>341</v>
       </c>
@@ -7005,7 +7008,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="14.4">
+    <row r="236" spans="1:2" ht="14.25">
       <c r="A236" s="34" t="s">
         <v>342</v>
       </c>
@@ -7014,7 +7017,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="14.4">
+    <row r="237" spans="1:2" ht="14.25">
       <c r="A237" s="34" t="s">
         <v>343</v>
       </c>
@@ -7023,7 +7026,7 @@
         <v>0.64499999999999991</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="14.4">
+    <row r="238" spans="1:2" ht="14.25">
       <c r="A238" s="34" t="s">
         <v>344</v>
       </c>
@@ -7032,7 +7035,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="14.4">
+    <row r="239" spans="1:2" ht="14.25">
       <c r="A239" s="32" t="s">
         <v>345</v>
       </c>
@@ -7040,7 +7043,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="14.4">
+    <row r="240" spans="1:2" ht="14.25">
       <c r="A240" s="32" t="s">
         <v>346</v>
       </c>
@@ -7048,7 +7051,7 @@
         <v>1.1500000000000001</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="14.4">
+    <row r="241" spans="1:2" ht="14.25">
       <c r="A241" s="32" t="s">
         <v>347</v>
       </c>
@@ -7056,7 +7059,7 @@
         <v>1.7500000000000002</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="14.4">
+    <row r="242" spans="1:2" ht="14.25">
       <c r="A242" s="32" t="s">
         <v>348</v>
       </c>
@@ -7064,7 +7067,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="14.4">
+    <row r="243" spans="1:2" ht="14.25">
       <c r="A243" s="32" t="s">
         <v>349</v>
       </c>
@@ -7072,7 +7075,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="14.4">
+    <row r="244" spans="1:2" ht="14.25">
       <c r="A244" s="32" t="s">
         <v>350</v>
       </c>
@@ -7080,7 +7083,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="14.4">
+    <row r="245" spans="1:2" ht="14.25">
       <c r="A245" s="32" t="s">
         <v>351</v>
       </c>
@@ -7088,7 +7091,7 @@
         <v>4.1499999999999995</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="14.4">
+    <row r="246" spans="1:2" ht="14.25">
       <c r="A246" s="32" t="s">
         <v>352</v>
       </c>
@@ -7096,7 +7099,7 @@
         <v>4.7499999999999991</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="14.4">
+    <row r="247" spans="1:2" ht="14.25">
       <c r="A247" s="32" t="s">
         <v>353</v>
       </c>
@@ -7104,7 +7107,7 @@
         <v>5.3499999999999988</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="14.4">
+    <row r="248" spans="1:2" ht="14.25">
       <c r="A248" s="32" t="s">
         <v>354</v>
       </c>
@@ -7112,7 +7115,7 @@
         <v>5.9499999999999984</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="14.4">
+    <row r="249" spans="1:2" ht="14.25">
       <c r="A249" s="33" t="s">
         <v>355</v>
       </c>
@@ -7121,7 +7124,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="14.4">
+    <row r="250" spans="1:2" ht="14.25">
       <c r="A250" s="33" t="s">
         <v>356</v>
       </c>
@@ -7130,7 +7133,7 @@
         <v>0.57500000000000007</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="14.4">
+    <row r="251" spans="1:2" ht="14.25">
       <c r="A251" s="33" t="s">
         <v>357</v>
       </c>
@@ -7139,7 +7142,7 @@
         <v>0.87500000000000011</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="14.4">
+    <row r="252" spans="1:2" ht="14.25">
       <c r="A252" s="33" t="s">
         <v>358</v>
       </c>
@@ -7148,7 +7151,7 @@
         <v>1.175</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="14.4">
+    <row r="253" spans="1:2" ht="14.25">
       <c r="A253" s="33" t="s">
         <v>359</v>
       </c>
@@ -7157,7 +7160,7 @@
         <v>1.4750000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="14.4">
+    <row r="254" spans="1:2" ht="14.25">
       <c r="A254" s="33" t="s">
         <v>360</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>1.7749999999999999</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="14.4">
+    <row r="255" spans="1:2" ht="14.25">
       <c r="A255" s="33" t="s">
         <v>361</v>
       </c>
@@ -7175,7 +7178,7 @@
         <v>2.0749999999999997</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="14.4">
+    <row r="256" spans="1:2" ht="14.25">
       <c r="A256" s="33" t="s">
         <v>362</v>
       </c>
@@ -7184,7 +7187,7 @@
         <v>2.3749999999999996</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="14.4">
+    <row r="257" spans="1:2" ht="14.25">
       <c r="A257" s="33" t="s">
         <v>363</v>
       </c>
@@ -7193,7 +7196,7 @@
         <v>2.6749999999999994</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="14.4">
+    <row r="258" spans="1:2" ht="14.25">
       <c r="A258" s="33" t="s">
         <v>364</v>
       </c>
@@ -7202,7 +7205,7 @@
         <v>2.9749999999999992</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="14.4">
+    <row r="259" spans="1:2" ht="14.25">
       <c r="A259" s="34" t="s">
         <v>365</v>
       </c>
@@ -7211,7 +7214,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="14.4">
+    <row r="260" spans="1:2" ht="14.25">
       <c r="A260" s="34" t="s">
         <v>366</v>
       </c>
@@ -7220,7 +7223,7 @@
         <v>0.34500000000000003</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="14.4">
+    <row r="261" spans="1:2" ht="14.25">
       <c r="A261" s="34" t="s">
         <v>367</v>
       </c>
@@ -7229,7 +7232,7 @@
         <v>0.52500000000000002</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="14.4">
+    <row r="262" spans="1:2" ht="14.25">
       <c r="A262" s="34" t="s">
         <v>368</v>
       </c>
@@ -7238,7 +7241,7 @@
         <v>0.70499999999999996</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="14.4">
+    <row r="263" spans="1:2" ht="14.25">
       <c r="A263" s="34" t="s">
         <v>369</v>
       </c>
@@ -7247,7 +7250,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="14.4">
+    <row r="264" spans="1:2" ht="14.25">
       <c r="A264" s="34" t="s">
         <v>370</v>
       </c>
@@ -7256,7 +7259,7 @@
         <v>1.0649999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="14.4">
+    <row r="265" spans="1:2" ht="14.25">
       <c r="A265" s="34" t="s">
         <v>371</v>
       </c>
@@ -7265,7 +7268,7 @@
         <v>1.2449999999999999</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="14.4">
+    <row r="266" spans="1:2" ht="14.25">
       <c r="A266" s="34" t="s">
         <v>372</v>
       </c>
@@ -7274,7 +7277,7 @@
         <v>1.4249999999999996</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="14.4">
+    <row r="267" spans="1:2" ht="14.25">
       <c r="A267" s="34" t="s">
         <v>373</v>
       </c>
@@ -7283,7 +7286,7 @@
         <v>1.6049999999999995</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="14.4">
+    <row r="268" spans="1:2" ht="14.25">
       <c r="A268" s="34" t="s">
         <v>374</v>
       </c>
@@ -7292,7 +7295,7 @@
         <v>1.7849999999999995</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="14.4">
+    <row r="269" spans="1:2" ht="14.25">
       <c r="A269" s="32" t="s">
         <v>375</v>
       </c>
@@ -7300,7 +7303,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="14.4">
+    <row r="270" spans="1:2" ht="14.25">
       <c r="A270" s="32" t="s">
         <v>379</v>
       </c>
@@ -7308,7 +7311,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="14.4">
+    <row r="271" spans="1:2" ht="14.25">
       <c r="A271" s="32" t="s">
         <v>380</v>
       </c>
@@ -7316,7 +7319,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="14.4">
+    <row r="272" spans="1:2" ht="14.25">
       <c r="A272" s="32" t="s">
         <v>381</v>
       </c>
@@ -7324,7 +7327,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="14.4">
+    <row r="273" spans="1:2" ht="14.25">
       <c r="A273" s="32" t="s">
         <v>382</v>
       </c>
@@ -7332,7 +7335,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="14.4">
+    <row r="274" spans="1:2" ht="14.25">
       <c r="A274" s="32" t="s">
         <v>384</v>
       </c>
@@ -7340,7 +7343,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="14.4">
+    <row r="275" spans="1:2" ht="14.25">
       <c r="A275" s="32" t="s">
         <v>383</v>
       </c>
@@ -7348,7 +7351,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="14.4">
+    <row r="276" spans="1:2" ht="14.25">
       <c r="A276" s="32" t="s">
         <v>385</v>
       </c>
@@ -7356,7 +7359,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="14.4">
+    <row r="277" spans="1:2" ht="14.25">
       <c r="A277" s="32" t="s">
         <v>386</v>
       </c>
@@ -7364,7 +7367,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="14.4">
+    <row r="278" spans="1:2" ht="14.25">
       <c r="A278" s="32" t="s">
         <v>387</v>
       </c>
@@ -7372,7 +7375,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="14.4">
+    <row r="279" spans="1:2" ht="14.25">
       <c r="A279" s="32" t="s">
         <v>388</v>
       </c>
@@ -7380,7 +7383,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="14.4">
+    <row r="280" spans="1:2" ht="14.25">
       <c r="A280" s="32" t="s">
         <v>376</v>
       </c>
@@ -7388,7 +7391,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="14.4">
+    <row r="281" spans="1:2" ht="14.25">
       <c r="A281" s="32" t="s">
         <v>377</v>
       </c>
@@ -7396,7 +7399,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="14.4">
+    <row r="282" spans="1:2" ht="14.25">
       <c r="A282" s="32" t="s">
         <v>378</v>
       </c>
@@ -7404,7 +7407,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="14.4">
+    <row r="283" spans="1:2" ht="14.25">
       <c r="A283" s="32" t="s">
         <v>389</v>
       </c>
@@ -7412,7 +7415,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="14.4">
+    <row r="284" spans="1:2" ht="14.25">
       <c r="A284" s="33" t="s">
         <v>390</v>
       </c>
@@ -7421,7 +7424,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="14.4">
+    <row r="285" spans="1:2" ht="14.25">
       <c r="A285" s="33" t="s">
         <v>391</v>
       </c>
@@ -7430,7 +7433,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="14.4">
+    <row r="286" spans="1:2" ht="14.25">
       <c r="A286" s="33" t="s">
         <v>392</v>
       </c>
@@ -7439,7 +7442,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="14.4">
+    <row r="287" spans="1:2" ht="14.25">
       <c r="A287" s="33" t="s">
         <v>393</v>
       </c>
@@ -7448,7 +7451,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="14.4">
+    <row r="288" spans="1:2" ht="14.25">
       <c r="A288" s="33" t="s">
         <v>394</v>
       </c>
@@ -7457,7 +7460,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="14.4">
+    <row r="289" spans="1:2" ht="14.25">
       <c r="A289" s="33" t="s">
         <v>395</v>
       </c>
@@ -7466,7 +7469,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="14.4">
+    <row r="290" spans="1:2" ht="14.25">
       <c r="A290" s="33" t="s">
         <v>396</v>
       </c>
@@ -7475,7 +7478,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="14.4">
+    <row r="291" spans="1:2" ht="14.25">
       <c r="A291" s="33" t="s">
         <v>397</v>
       </c>
@@ -7484,7 +7487,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="14.4">
+    <row r="292" spans="1:2" ht="14.25">
       <c r="A292" s="33" t="s">
         <v>398</v>
       </c>
@@ -7493,7 +7496,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="14.4">
+    <row r="293" spans="1:2" ht="14.25">
       <c r="A293" s="33" t="s">
         <v>399</v>
       </c>
@@ -7502,7 +7505,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:2" ht="14.4">
+    <row r="294" spans="1:2" ht="14.25">
       <c r="A294" s="33" t="s">
         <v>400</v>
       </c>
@@ -7511,7 +7514,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="14.4">
+    <row r="295" spans="1:2" ht="14.25">
       <c r="A295" s="33" t="s">
         <v>401</v>
       </c>
@@ -7520,7 +7523,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="14.4">
+    <row r="296" spans="1:2" ht="14.25">
       <c r="A296" s="33" t="s">
         <v>402</v>
       </c>
@@ -7529,7 +7532,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="297" spans="1:2" ht="14.4">
+    <row r="297" spans="1:2" ht="14.25">
       <c r="A297" s="33" t="s">
         <v>403</v>
       </c>
@@ -7538,7 +7541,7 @@
         <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="298" spans="1:2" ht="14.4">
+    <row r="298" spans="1:2" ht="14.25">
       <c r="A298" s="33" t="s">
         <v>404</v>
       </c>
@@ -7547,7 +7550,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="14.4">
+    <row r="299" spans="1:2" ht="14.25">
       <c r="A299" s="34" t="s">
         <v>405</v>
       </c>
@@ -7556,7 +7559,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="14.4">
+    <row r="300" spans="1:2" ht="14.25">
       <c r="A300" s="34" t="s">
         <v>406</v>
       </c>
@@ -7565,7 +7568,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:2" ht="14.4">
+    <row r="301" spans="1:2" ht="14.25">
       <c r="A301" s="34" t="s">
         <v>407</v>
       </c>
@@ -7574,7 +7577,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="14.4">
+    <row r="302" spans="1:2" ht="14.25">
       <c r="A302" s="34" t="s">
         <v>408</v>
       </c>
@@ -7583,7 +7586,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="14.4">
+    <row r="303" spans="1:2" ht="14.25">
       <c r="A303" s="34" t="s">
         <v>409</v>
       </c>
@@ -7592,7 +7595,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="14.4">
+    <row r="304" spans="1:2" ht="14.25">
       <c r="A304" s="34" t="s">
         <v>410</v>
       </c>
@@ -7601,7 +7604,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="14.4">
+    <row r="305" spans="1:2" ht="14.25">
       <c r="A305" s="34" t="s">
         <v>411</v>
       </c>
@@ -7610,7 +7613,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:2" ht="14.4">
+    <row r="306" spans="1:2" ht="14.25">
       <c r="A306" s="34" t="s">
         <v>412</v>
       </c>
@@ -7619,7 +7622,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="307" spans="1:2" ht="14.4">
+    <row r="307" spans="1:2" ht="14.25">
       <c r="A307" s="34" t="s">
         <v>413</v>
       </c>
@@ -7628,7 +7631,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="308" spans="1:2" ht="14.4">
+    <row r="308" spans="1:2" ht="14.25">
       <c r="A308" s="34" t="s">
         <v>414</v>
       </c>
@@ -7637,7 +7640,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:2" ht="14.4">
+    <row r="309" spans="1:2" ht="14.25">
       <c r="A309" s="34" t="s">
         <v>415</v>
       </c>
@@ -7646,7 +7649,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="310" spans="1:2" ht="14.4">
+    <row r="310" spans="1:2" ht="14.25">
       <c r="A310" s="34" t="s">
         <v>416</v>
       </c>
@@ -7655,7 +7658,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="311" spans="1:2" ht="14.4">
+    <row r="311" spans="1:2" ht="14.25">
       <c r="A311" s="34" t="s">
         <v>417</v>
       </c>
@@ -7664,7 +7667,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="312" spans="1:2" ht="14.4">
+    <row r="312" spans="1:2" ht="14.25">
       <c r="A312" s="34" t="s">
         <v>418</v>
       </c>
@@ -7673,7 +7676,7 @@
         <v>0.435</v>
       </c>
     </row>
-    <row r="313" spans="1:2" ht="14.4">
+    <row r="313" spans="1:2" ht="14.25">
       <c r="A313" s="34" t="s">
         <v>419</v>
       </c>
@@ -7682,7 +7685,7 @@
         <v>0.49499999999999994</v>
       </c>
     </row>
-    <row r="314" spans="1:2" ht="14.4">
+    <row r="314" spans="1:2" ht="14.25">
       <c r="A314" s="32" t="s">
         <v>423</v>
       </c>
@@ -7690,7 +7693,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="315" spans="1:2" ht="14.4">
+    <row r="315" spans="1:2" ht="14.25">
       <c r="A315" s="32" t="s">
         <v>424</v>
       </c>
@@ -7698,7 +7701,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="316" spans="1:2" ht="14.4">
+    <row r="316" spans="1:2" ht="14.25">
       <c r="A316" s="32" t="s">
         <v>425</v>
       </c>
@@ -7706,7 +7709,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="317" spans="1:2" ht="14.4">
+    <row r="317" spans="1:2" ht="14.25">
       <c r="A317" s="32" t="s">
         <v>426</v>
       </c>
@@ -7714,7 +7717,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="318" spans="1:2" ht="14.4">
+    <row r="318" spans="1:2" ht="14.25">
       <c r="A318" s="32" t="s">
         <v>427</v>
       </c>
@@ -7722,7 +7725,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="319" spans="1:2" ht="14.4">
+    <row r="319" spans="1:2" ht="14.25">
       <c r="A319" s="32" t="s">
         <v>428</v>
       </c>
@@ -7730,7 +7733,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="320" spans="1:2" ht="14.4">
+    <row r="320" spans="1:2" ht="14.25">
       <c r="A320" s="32" t="s">
         <v>429</v>
       </c>
@@ -7738,7 +7741,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="14.4">
+    <row r="321" spans="1:2" ht="14.25">
       <c r="A321" s="32" t="s">
         <v>430</v>
       </c>
@@ -7746,7 +7749,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="14.4">
+    <row r="322" spans="1:2" ht="14.25">
       <c r="A322" s="32" t="s">
         <v>431</v>
       </c>
@@ -7754,7 +7757,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="14.4">
+    <row r="323" spans="1:2" ht="14.25">
       <c r="A323" s="32" t="s">
         <v>432</v>
       </c>
@@ -7762,7 +7765,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="14.4">
+    <row r="324" spans="1:2" ht="14.25">
       <c r="A324" s="32" t="s">
         <v>433</v>
       </c>
@@ -7770,7 +7773,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="14.4">
+    <row r="325" spans="1:2" ht="14.25">
       <c r="A325" s="32" t="s">
         <v>434</v>
       </c>
@@ -7778,7 +7781,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="14.4">
+    <row r="326" spans="1:2" ht="14.25">
       <c r="A326" s="32" t="s">
         <v>435</v>
       </c>
@@ -7786,7 +7789,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="14.4">
+    <row r="327" spans="1:2" ht="14.25">
       <c r="A327" s="32" t="s">
         <v>436</v>
       </c>
@@ -7794,7 +7797,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="14.4">
+    <row r="328" spans="1:2" ht="14.25">
       <c r="A328" s="32" t="s">
         <v>437</v>
       </c>
@@ -7802,7 +7805,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="14.4">
+    <row r="329" spans="1:2" ht="14.25">
       <c r="A329" s="32" t="s">
         <v>438</v>
       </c>
@@ -7810,7 +7813,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="14.4">
+    <row r="330" spans="1:2" ht="14.25">
       <c r="A330" s="32" t="s">
         <v>439</v>
       </c>
@@ -7818,7 +7821,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="14.4">
+    <row r="331" spans="1:2" ht="14.25">
       <c r="A331" s="32" t="s">
         <v>440</v>
       </c>
@@ -7826,7 +7829,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="14.4">
+    <row r="332" spans="1:2" ht="14.25">
       <c r="A332" s="32" t="s">
         <v>441</v>
       </c>
@@ -7834,7 +7837,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="14.4">
+    <row r="333" spans="1:2" ht="14.25">
       <c r="A333" s="32" t="s">
         <v>442</v>
       </c>
@@ -7842,7 +7845,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="14.4">
+    <row r="334" spans="1:2" ht="14.25">
       <c r="A334" s="32" t="s">
         <v>443</v>
       </c>
@@ -7850,7 +7853,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="14.4">
+    <row r="335" spans="1:2" ht="14.25">
       <c r="A335" s="32" t="s">
         <v>444</v>
       </c>
@@ -7858,7 +7861,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="14.4">
+    <row r="336" spans="1:2" ht="14.25">
       <c r="A336" s="32" t="s">
         <v>445</v>
       </c>
@@ -7866,7 +7869,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="14.4">
+    <row r="337" spans="1:2" ht="14.25">
       <c r="A337" s="32" t="s">
         <v>420</v>
       </c>
@@ -7874,7 +7877,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="14.4">
+    <row r="338" spans="1:2" ht="14.25">
       <c r="A338" s="32" t="s">
         <v>446</v>
       </c>
@@ -7882,7 +7885,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="14.4">
+    <row r="339" spans="1:2" ht="14.25">
       <c r="A339" s="32" t="s">
         <v>447</v>
       </c>
@@ -7890,7 +7893,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="14.4">
+    <row r="340" spans="1:2" ht="14.25">
       <c r="A340" s="32" t="s">
         <v>421</v>
       </c>
@@ -7898,7 +7901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="14.4">
+    <row r="341" spans="1:2" ht="14.25">
       <c r="A341" s="32" t="s">
         <v>422</v>
       </c>
@@ -7906,7 +7909,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="14.4">
+    <row r="342" spans="1:2" ht="14.25">
       <c r="A342" s="33" t="s">
         <v>448</v>
       </c>
@@ -7915,7 +7918,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="14.4">
+    <row r="343" spans="1:2" ht="14.25">
       <c r="A343" s="33" t="s">
         <v>449</v>
       </c>
@@ -7924,7 +7927,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="14.4">
+    <row r="344" spans="1:2" ht="14.25">
       <c r="A344" s="33" t="s">
         <v>450</v>
       </c>
@@ -7933,7 +7936,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="14.4">
+    <row r="345" spans="1:2" ht="14.25">
       <c r="A345" s="33" t="s">
         <v>451</v>
       </c>
@@ -7942,7 +7945,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="14.4">
+    <row r="346" spans="1:2" ht="14.25">
       <c r="A346" s="33" t="s">
         <v>452</v>
       </c>
@@ -7951,7 +7954,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="14.4">
+    <row r="347" spans="1:2" ht="14.25">
       <c r="A347" s="33" t="s">
         <v>453</v>
       </c>
@@ -7960,7 +7963,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="14.4">
+    <row r="348" spans="1:2" ht="14.25">
       <c r="A348" s="33" t="s">
         <v>454</v>
       </c>
@@ -7969,7 +7972,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="14.4">
+    <row r="349" spans="1:2" ht="14.25">
       <c r="A349" s="33" t="s">
         <v>455</v>
       </c>
@@ -7978,7 +7981,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="14.4">
+    <row r="350" spans="1:2" ht="14.25">
       <c r="A350" s="33" t="s">
         <v>456</v>
       </c>
@@ -7987,7 +7990,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="14.4">
+    <row r="351" spans="1:2" ht="14.25">
       <c r="A351" s="33" t="s">
         <v>457</v>
       </c>
@@ -7996,7 +7999,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="14.4">
+    <row r="352" spans="1:2" ht="14.25">
       <c r="A352" s="33" t="s">
         <v>458</v>
       </c>
@@ -8005,7 +8008,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="14.4">
+    <row r="353" spans="1:2" ht="14.25">
       <c r="A353" s="33" t="s">
         <v>459</v>
       </c>
@@ -8014,7 +8017,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="14.4">
+    <row r="354" spans="1:2" ht="14.25">
       <c r="A354" s="33" t="s">
         <v>460</v>
       </c>
@@ -8023,7 +8026,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="14.4">
+    <row r="355" spans="1:2" ht="14.25">
       <c r="A355" s="33" t="s">
         <v>461</v>
       </c>
@@ -8032,7 +8035,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="14.4">
+    <row r="356" spans="1:2" ht="14.25">
       <c r="A356" s="33" t="s">
         <v>462</v>
       </c>
@@ -8041,7 +8044,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="14.4">
+    <row r="357" spans="1:2" ht="14.25">
       <c r="A357" s="33" t="s">
         <v>463</v>
       </c>
@@ -8050,7 +8053,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="14.4">
+    <row r="358" spans="1:2" ht="14.25">
       <c r="A358" s="33" t="s">
         <v>464</v>
       </c>
@@ -8059,7 +8062,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="14.4">
+    <row r="359" spans="1:2" ht="14.25">
       <c r="A359" s="33" t="s">
         <v>465</v>
       </c>
@@ -8068,7 +8071,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="14.4">
+    <row r="360" spans="1:2" ht="14.25">
       <c r="A360" s="33" t="s">
         <v>466</v>
       </c>
@@ -8077,7 +8080,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="14.4">
+    <row r="361" spans="1:2" ht="14.25">
       <c r="A361" s="33" t="s">
         <v>467</v>
       </c>
@@ -8086,7 +8089,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="14.4">
+    <row r="362" spans="1:2" ht="14.25">
       <c r="A362" s="33" t="s">
         <v>468</v>
       </c>
@@ -8095,7 +8098,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="14.4">
+    <row r="363" spans="1:2" ht="14.25">
       <c r="A363" s="33" t="s">
         <v>469</v>
       </c>
@@ -8104,7 +8107,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="14.4">
+    <row r="364" spans="1:2" ht="14.25">
       <c r="A364" s="33" t="s">
         <v>470</v>
       </c>
@@ -8113,7 +8116,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="14.4">
+    <row r="365" spans="1:2" ht="14.25">
       <c r="A365" s="33" t="s">
         <v>471</v>
       </c>
@@ -8122,7 +8125,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="14.4">
+    <row r="366" spans="1:2" ht="14.25">
       <c r="A366" s="33" t="s">
         <v>472</v>
       </c>
@@ -8131,7 +8134,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="14.4">
+    <row r="367" spans="1:2" ht="14.25">
       <c r="A367" s="33" t="s">
         <v>473</v>
       </c>
@@ -8140,7 +8143,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="368" spans="1:2" ht="14.4">
+    <row r="368" spans="1:2" ht="14.25">
       <c r="A368" s="33" t="s">
         <v>474</v>
       </c>
@@ -8149,7 +8152,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="369" spans="1:2" ht="14.4">
+    <row r="369" spans="1:2" ht="14.25">
       <c r="A369" s="33" t="s">
         <v>475</v>
       </c>
@@ -8158,7 +8161,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="370" spans="1:2" ht="14.4">
+    <row r="370" spans="1:2" ht="14.25">
       <c r="A370" s="34" t="s">
         <v>476</v>
       </c>
@@ -8167,7 +8170,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:2" ht="14.4">
+    <row r="371" spans="1:2" ht="14.25">
       <c r="A371" s="34" t="s">
         <v>477</v>
       </c>
@@ -8176,7 +8179,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="372" spans="1:2" ht="14.4">
+    <row r="372" spans="1:2" ht="14.25">
       <c r="A372" s="34" t="s">
         <v>478</v>
       </c>
@@ -8185,7 +8188,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="373" spans="1:2" ht="14.4">
+    <row r="373" spans="1:2" ht="14.25">
       <c r="A373" s="34" t="s">
         <v>479</v>
       </c>
@@ -8194,7 +8197,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="374" spans="1:2" ht="14.4">
+    <row r="374" spans="1:2" ht="14.25">
       <c r="A374" s="34" t="s">
         <v>480</v>
       </c>
@@ -8203,7 +8206,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="375" spans="1:2" ht="14.4">
+    <row r="375" spans="1:2" ht="14.25">
       <c r="A375" s="34" t="s">
         <v>481</v>
       </c>
@@ -8212,7 +8215,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="376" spans="1:2" ht="14.4">
+    <row r="376" spans="1:2" ht="14.25">
       <c r="A376" s="34" t="s">
         <v>482</v>
       </c>
@@ -8221,7 +8224,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="377" spans="1:2" ht="14.4">
+    <row r="377" spans="1:2" ht="14.25">
       <c r="A377" s="34" t="s">
         <v>483</v>
       </c>
@@ -8230,7 +8233,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="378" spans="1:2" ht="14.4">
+    <row r="378" spans="1:2" ht="14.25">
       <c r="A378" s="34" t="s">
         <v>484</v>
       </c>
@@ -8239,7 +8242,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="379" spans="1:2" ht="14.4">
+    <row r="379" spans="1:2" ht="14.25">
       <c r="A379" s="34" t="s">
         <v>485</v>
       </c>
@@ -8248,7 +8251,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="380" spans="1:2" ht="14.4">
+    <row r="380" spans="1:2" ht="14.25">
       <c r="A380" s="34" t="s">
         <v>486</v>
       </c>
@@ -8257,7 +8260,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="381" spans="1:2" ht="14.4">
+    <row r="381" spans="1:2" ht="14.25">
       <c r="A381" s="34" t="s">
         <v>487</v>
       </c>
@@ -8266,7 +8269,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="382" spans="1:2" ht="14.4">
+    <row r="382" spans="1:2" ht="14.25">
       <c r="A382" s="34" t="s">
         <v>488</v>
       </c>
@@ -8275,7 +8278,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="383" spans="1:2" ht="14.4">
+    <row r="383" spans="1:2" ht="14.25">
       <c r="A383" s="34" t="s">
         <v>489</v>
       </c>
@@ -8284,7 +8287,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="384" spans="1:2" ht="14.4">
+    <row r="384" spans="1:2" ht="14.25">
       <c r="A384" s="34" t="s">
         <v>490</v>
       </c>
@@ -8293,7 +8296,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="385" spans="1:2" ht="14.4">
+    <row r="385" spans="1:2" ht="14.25">
       <c r="A385" s="34" t="s">
         <v>491</v>
       </c>
@@ -8302,7 +8305,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="386" spans="1:2" ht="14.4">
+    <row r="386" spans="1:2" ht="14.25">
       <c r="A386" s="34" t="s">
         <v>492</v>
       </c>
@@ -8311,7 +8314,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="387" spans="1:2" ht="14.4">
+    <row r="387" spans="1:2" ht="14.25">
       <c r="A387" s="34" t="s">
         <v>493</v>
       </c>
@@ -8320,7 +8323,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="388" spans="1:2" ht="14.4">
+    <row r="388" spans="1:2" ht="14.25">
       <c r="A388" s="34" t="s">
         <v>494</v>
       </c>
@@ -8329,7 +8332,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="389" spans="1:2" ht="14.4">
+    <row r="389" spans="1:2" ht="14.25">
       <c r="A389" s="34" t="s">
         <v>495</v>
       </c>
@@ -8338,7 +8341,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="390" spans="1:2" ht="14.4">
+    <row r="390" spans="1:2" ht="14.25">
       <c r="A390" s="34" t="s">
         <v>496</v>
       </c>
@@ -8347,7 +8350,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="391" spans="1:2" ht="14.4">
+    <row r="391" spans="1:2" ht="14.25">
       <c r="A391" s="34" t="s">
         <v>497</v>
       </c>
@@ -8356,7 +8359,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="392" spans="1:2" ht="14.4">
+    <row r="392" spans="1:2" ht="14.25">
       <c r="A392" s="34" t="s">
         <v>498</v>
       </c>
@@ -8365,7 +8368,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="393" spans="1:2" ht="14.4">
+    <row r="393" spans="1:2" ht="14.25">
       <c r="A393" s="34" t="s">
         <v>499</v>
       </c>
@@ -8374,7 +8377,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="394" spans="1:2" ht="14.4">
+    <row r="394" spans="1:2" ht="14.25">
       <c r="A394" s="34" t="s">
         <v>500</v>
       </c>
@@ -8383,7 +8386,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="395" spans="1:2" ht="14.4">
+    <row r="395" spans="1:2" ht="14.25">
       <c r="A395" s="34" t="s">
         <v>501</v>
       </c>
@@ -8392,7 +8395,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="396" spans="1:2" ht="14.4">
+    <row r="396" spans="1:2" ht="14.25">
       <c r="A396" s="34" t="s">
         <v>502</v>
       </c>
@@ -8401,7 +8404,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="397" spans="1:2" ht="14.4">
+    <row r="397" spans="1:2" ht="14.25">
       <c r="A397" s="34" t="s">
         <v>503</v>
       </c>
@@ -8410,7 +8413,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="398" spans="1:2" ht="14.4">
+    <row r="398" spans="1:2" ht="14.25">
       <c r="A398" s="32" t="s">
         <v>504</v>
       </c>
@@ -8418,7 +8421,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="399" spans="1:2" ht="14.4">
+    <row r="399" spans="1:2" ht="14.25">
       <c r="A399" s="32" t="s">
         <v>505</v>
       </c>
@@ -8426,7 +8429,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="400" spans="1:2" ht="14.4">
+    <row r="400" spans="1:2" ht="14.25">
       <c r="A400" s="32" t="s">
         <v>506</v>
       </c>
@@ -8434,7 +8437,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="401" spans="1:2" ht="14.4">
+    <row r="401" spans="1:2" ht="14.25">
       <c r="A401" s="32" t="s">
         <v>507</v>
       </c>
@@ -8442,7 +8445,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="402" spans="1:2" ht="14.4">
+    <row r="402" spans="1:2" ht="14.25">
       <c r="A402" s="32" t="s">
         <v>508</v>
       </c>
@@ -8450,7 +8453,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="403" spans="1:2" ht="14.4">
+    <row r="403" spans="1:2" ht="14.25">
       <c r="A403" s="32" t="s">
         <v>509</v>
       </c>
@@ -8458,7 +8461,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="404" spans="1:2" ht="14.4">
+    <row r="404" spans="1:2" ht="14.25">
       <c r="A404" s="32" t="s">
         <v>510</v>
       </c>
@@ -8466,7 +8469,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="405" spans="1:2" ht="14.4">
+    <row r="405" spans="1:2" ht="14.25">
       <c r="A405" s="32" t="s">
         <v>511</v>
       </c>
@@ -8474,7 +8477,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="406" spans="1:2" ht="14.4">
+    <row r="406" spans="1:2" ht="14.25">
       <c r="A406" s="32" t="s">
         <v>512</v>
       </c>
@@ -8482,7 +8485,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="407" spans="1:2" ht="14.4">
+    <row r="407" spans="1:2" ht="14.25">
       <c r="A407" s="32" t="s">
         <v>513</v>
       </c>
@@ -8490,7 +8493,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="408" spans="1:2" ht="14.4">
+    <row r="408" spans="1:2" ht="14.25">
       <c r="A408" s="32" t="s">
         <v>514</v>
       </c>
@@ -8498,7 +8501,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="409" spans="1:2" ht="14.4">
+    <row r="409" spans="1:2" ht="14.25">
       <c r="A409" s="32" t="s">
         <v>515</v>
       </c>
@@ -8506,7 +8509,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="410" spans="1:2" ht="14.4">
+    <row r="410" spans="1:2" ht="14.25">
       <c r="A410" s="32" t="s">
         <v>29</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="411" spans="1:2" ht="14.4">
+    <row r="411" spans="1:2" ht="14.25">
       <c r="A411" s="32" t="s">
         <v>104</v>
       </c>
@@ -8522,7 +8525,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="412" spans="1:2" ht="14.4">
+    <row r="412" spans="1:2" ht="14.25">
       <c r="A412" s="32" t="s">
         <v>36</v>
       </c>
@@ -8530,7 +8533,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="413" spans="1:2" ht="14.4">
+    <row r="413" spans="1:2" ht="14.25">
       <c r="A413" s="32" t="s">
         <v>105</v>
       </c>
@@ -8538,7 +8541,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="414" spans="1:2" ht="14.4">
+    <row r="414" spans="1:2" ht="14.25">
       <c r="A414" s="32" t="s">
         <v>37</v>
       </c>
@@ -8546,7 +8549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:2" ht="14.4">
+    <row r="415" spans="1:2" ht="14.25">
       <c r="A415" s="32" t="s">
         <v>106</v>
       </c>
@@ -8554,7 +8557,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:2" ht="14.4">
+    <row r="416" spans="1:2" ht="14.25">
       <c r="A416" s="32" t="s">
         <v>517</v>
       </c>
@@ -8562,7 +8565,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="417" spans="1:2" ht="14.4">
+    <row r="417" spans="1:2" ht="14.25">
       <c r="A417" s="32" t="s">
         <v>516</v>
       </c>
@@ -8570,7 +8573,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="418" spans="1:2" ht="14.4">
+    <row r="418" spans="1:2" ht="14.25">
       <c r="A418" s="32" t="s">
         <v>518</v>
       </c>
@@ -8578,7 +8581,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="419" spans="1:2" ht="14.4">
+    <row r="419" spans="1:2" ht="14.25">
       <c r="A419" s="32" t="s">
         <v>519</v>
       </c>
@@ -8586,7 +8589,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="420" spans="1:2" ht="14.4">
+    <row r="420" spans="1:2" ht="14.25">
       <c r="A420" s="32" t="s">
         <v>520</v>
       </c>
@@ -8594,7 +8597,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="421" spans="1:2" ht="14.4">
+    <row r="421" spans="1:2" ht="14.25">
       <c r="A421" s="32" t="s">
         <v>521</v>
       </c>
@@ -8602,7 +8605,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="422" spans="1:2" ht="14.4">
+    <row r="422" spans="1:2" ht="14.25">
       <c r="A422" s="35" t="s">
         <v>111</v>
       </c>
@@ -8610,7 +8613,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="423" spans="1:2" ht="14.4">
+    <row r="423" spans="1:2" ht="14.25">
       <c r="A423" s="35" t="s">
         <v>112</v>
       </c>
@@ -8618,7 +8621,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="424" spans="1:2" ht="14.4">
+    <row r="424" spans="1:2" ht="14.25">
       <c r="A424" s="35" t="s">
         <v>113</v>
       </c>
@@ -8626,7 +8629,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="425" spans="1:2" ht="14.4">
+    <row r="425" spans="1:2" ht="14.25">
       <c r="A425" s="35" t="s">
         <v>114</v>
       </c>
@@ -8634,7 +8637,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="426" spans="1:2" ht="14.4">
+    <row r="426" spans="1:2" ht="14.25">
       <c r="A426" s="35" t="s">
         <v>115</v>
       </c>
@@ -8642,7 +8645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:2" ht="14.4">
+    <row r="427" spans="1:2" ht="14.25">
       <c r="A427" s="35" t="s">
         <v>116</v>
       </c>
@@ -8650,7 +8653,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="428" spans="1:2" ht="14.4">
+    <row r="428" spans="1:2" ht="14.25">
       <c r="A428" s="35" t="s">
         <v>117</v>
       </c>
@@ -8658,7 +8661,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="429" spans="1:2" ht="14.4">
+    <row r="429" spans="1:2" ht="14.25">
       <c r="A429" s="35" t="s">
         <v>118</v>
       </c>
@@ -8666,7 +8669,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="430" spans="1:2" ht="14.4">
+    <row r="430" spans="1:2" ht="14.25">
       <c r="A430" s="35" t="s">
         <v>119</v>
       </c>
@@ -8674,7 +8677,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="431" spans="1:2" ht="14.4">
+    <row r="431" spans="1:2" ht="14.25">
       <c r="A431" s="35" t="s">
         <v>120</v>
       </c>
@@ -8682,7 +8685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432" spans="1:2" ht="14.4">
+    <row r="432" spans="1:2" ht="14.25">
       <c r="A432" s="35" t="s">
         <v>199</v>
       </c>
@@ -8690,7 +8693,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="433" spans="1:2" ht="14.4">
+    <row r="433" spans="1:2" ht="14.25">
       <c r="A433" s="35" t="s">
         <v>200</v>
       </c>
@@ -8698,7 +8701,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="434" spans="1:2" ht="14.4">
+    <row r="434" spans="1:2" ht="14.25">
       <c r="A434" s="83" t="s">
         <v>39</v>
       </c>
@@ -8706,7 +8709,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="435" spans="1:2" ht="14.4">
+    <row r="435" spans="1:2" ht="14.25">
       <c r="A435" s="83" t="s">
         <v>40</v>
       </c>
@@ -8714,7 +8717,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="436" spans="1:2" ht="14.4">
+    <row r="436" spans="1:2" ht="14.25">
       <c r="A436" s="83" t="s">
         <v>41</v>
       </c>
@@ -8722,7 +8725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:2" ht="14.4">
+    <row r="437" spans="1:2" ht="14.25">
       <c r="A437" s="83" t="s">
         <v>42</v>
       </c>
@@ -8730,7 +8733,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="438" spans="1:2" ht="14.4">
+    <row r="438" spans="1:2" ht="14.25">
       <c r="A438" s="83" t="s">
         <v>100</v>
       </c>
@@ -8738,7 +8741,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="439" spans="1:2" ht="14.4">
+    <row r="439" spans="1:2" ht="14.25">
       <c r="A439" s="83" t="s">
         <v>43</v>
       </c>
@@ -8746,7 +8749,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="440" spans="1:2" ht="14.4">
+    <row r="440" spans="1:2" ht="14.25">
       <c r="A440" s="83" t="s">
         <v>44</v>
       </c>
@@ -8754,7 +8757,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="441" spans="1:2" ht="14.4">
+    <row r="441" spans="1:2" ht="14.25">
       <c r="A441" s="83" t="s">
         <v>45</v>
       </c>
@@ -8762,7 +8765,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="442" spans="1:2" ht="14.4">
+    <row r="442" spans="1:2" ht="14.25">
       <c r="A442" s="83" t="s">
         <v>46</v>
       </c>
@@ -8770,7 +8773,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="443" spans="1:2" ht="14.4">
+    <row r="443" spans="1:2" ht="14.25">
       <c r="A443" s="85" t="s">
         <v>58</v>
       </c>
@@ -8778,7 +8781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:2" ht="14.4">
+    <row r="444" spans="1:2" ht="14.25">
       <c r="A444" s="85" t="s">
         <v>59</v>
       </c>
@@ -8786,7 +8789,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="445" spans="1:2" ht="14.4">
+    <row r="445" spans="1:2" ht="14.25">
       <c r="A445" s="85" t="s">
         <v>60</v>
       </c>
@@ -8794,7 +8797,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="446" spans="1:2" ht="14.4">
+    <row r="446" spans="1:2" ht="14.25">
       <c r="A446" s="85" t="s">
         <v>61</v>
       </c>
@@ -8802,7 +8805,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="447" spans="1:2" ht="14.4">
+    <row r="447" spans="1:2" ht="14.25">
       <c r="A447" s="85" t="s">
         <v>131</v>
       </c>
@@ -8810,7 +8813,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="448" spans="1:2" ht="14.4">
+    <row r="448" spans="1:2" ht="14.25">
       <c r="A448" s="85" t="s">
         <v>62</v>
       </c>
@@ -8818,7 +8821,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="449" spans="1:2" ht="14.4">
+    <row r="449" spans="1:2" ht="14.25">
       <c r="A449" s="85" t="s">
         <v>63</v>
       </c>
@@ -8826,7 +8829,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="450" spans="1:2" ht="14.4">
+    <row r="450" spans="1:2" ht="14.25">
       <c r="A450" s="85" t="s">
         <v>64</v>
       </c>
@@ -8834,7 +8837,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="451" spans="1:2" ht="14.4">
+    <row r="451" spans="1:2" ht="14.25">
       <c r="A451" s="85" t="s">
         <v>65</v>
       </c>
@@ -8842,7 +8845,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="452" spans="1:2" ht="14.4">
+    <row r="452" spans="1:2" ht="14.25">
       <c r="A452" s="36" t="s">
         <v>66</v>
       </c>
@@ -8850,7 +8853,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="453" spans="1:2" ht="14.4">
+    <row r="453" spans="1:2" ht="14.25">
       <c r="A453" s="36" t="s">
         <v>67</v>
       </c>
@@ -8858,7 +8861,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="454" spans="1:2" ht="14.4">
+    <row r="454" spans="1:2" ht="14.25">
       <c r="A454" s="36" t="s">
         <v>68</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="455" spans="1:2" ht="14.4">
+    <row r="455" spans="1:2" ht="14.25">
       <c r="A455" s="36" t="s">
         <v>69</v>
       </c>
@@ -8874,7 +8877,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="456" spans="1:2" ht="14.4">
+    <row r="456" spans="1:2" ht="14.25">
       <c r="A456" s="36" t="s">
         <v>101</v>
       </c>
@@ -8882,7 +8885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" spans="1:2" ht="14.4">
+    <row r="457" spans="1:2" ht="14.25">
       <c r="A457" s="83" t="s">
         <v>50</v>
       </c>
@@ -8890,7 +8893,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="458" spans="1:2" ht="14.4">
+    <row r="458" spans="1:2" ht="14.25">
       <c r="A458" s="83" t="s">
         <v>51</v>
       </c>
@@ -8898,7 +8901,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="459" spans="1:2" ht="14.4">
+    <row r="459" spans="1:2" ht="14.25">
       <c r="A459" s="83" t="s">
         <v>52</v>
       </c>
@@ -8906,7 +8909,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="460" spans="1:2" ht="14.4">
+    <row r="460" spans="1:2" ht="14.25">
       <c r="A460" s="83" t="s">
         <v>53</v>
       </c>
@@ -8914,7 +8917,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="461" spans="1:2" ht="14.4">
+    <row r="461" spans="1:2" ht="14.25">
       <c r="A461" s="83" t="s">
         <v>54</v>
       </c>
@@ -8922,7 +8925,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="462" spans="1:2" ht="14.4">
+    <row r="462" spans="1:2" ht="14.25">
       <c r="A462" s="83" t="s">
         <v>55</v>
       </c>
@@ -8930,7 +8933,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="463" spans="1:2" ht="14.4">
+    <row r="463" spans="1:2" ht="14.25">
       <c r="A463" s="83" t="s">
         <v>102</v>
       </c>
@@ -8938,7 +8941,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="464" spans="1:2" ht="14.4">
+    <row r="464" spans="1:2" ht="14.25">
       <c r="A464" s="83" t="s">
         <v>56</v>
       </c>
@@ -8946,7 +8949,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="465" spans="1:2" ht="14.4">
+    <row r="465" spans="1:2" ht="14.25">
       <c r="A465" s="83" t="s">
         <v>57</v>
       </c>
@@ -8965,184 +8968,184 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E964F2-A890-4879-8403-994068130CEC}">
   <dimension ref="A5:U65"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" style="31" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" style="42" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" style="74" customWidth="1"/>
     <col min="5" max="19" width="8.6640625" style="42" customWidth="1"/>
-    <col min="20" max="20" width="11.5546875" style="42" customWidth="1"/>
-    <col min="21" max="21" width="12.88671875" style="42" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="42"/>
+    <col min="20" max="20" width="11.53125" style="42" customWidth="1"/>
+    <col min="21" max="21" width="12.86328125" style="42" customWidth="1"/>
+    <col min="22" max="16384" width="8.86328125" style="42"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" ht="13.8" thickBot="1"/>
-    <row r="6" spans="1:21">
-      <c r="A6" s="115" t="s">
+    <row r="5" spans="1:21" ht="13.15" thickBot="1"/>
+    <row r="6" spans="1:21" ht="13.15">
+      <c r="A6" s="113" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="116"/>
-      <c r="C6" s="117" t="s">
+      <c r="B6" s="114"/>
+      <c r="C6" s="115" t="s">
         <v>531</v>
       </c>
-      <c r="D6" s="118"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="119"/>
-      <c r="M6" s="119"/>
-      <c r="N6" s="119"/>
-      <c r="O6" s="119"/>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="119"/>
-      <c r="U6" s="120"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="121" t="s">
+      <c r="D6" s="116"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="117"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="117"/>
+      <c r="S6" s="117"/>
+      <c r="T6" s="117"/>
+      <c r="U6" s="118"/>
+    </row>
+    <row r="7" spans="1:21" ht="13.15">
+      <c r="A7" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="122"/>
-      <c r="C7" s="123" t="s">
+      <c r="B7" s="96"/>
+      <c r="C7" s="97" t="s">
         <v>537</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="125"/>
-      <c r="P7" s="125"/>
-      <c r="Q7" s="125"/>
-      <c r="R7" s="125"/>
-      <c r="S7" s="125"/>
-      <c r="T7" s="125"/>
-      <c r="U7" s="126"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="121" t="s">
+      <c r="D7" s="98"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="100"/>
+    </row>
+    <row r="8" spans="1:21" ht="13.15">
+      <c r="A8" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="122"/>
-      <c r="C8" s="123" t="s">
+      <c r="B8" s="96"/>
+      <c r="C8" s="97" t="s">
         <v>536</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="125"/>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="125"/>
-      <c r="Q8" s="125"/>
-      <c r="R8" s="125"/>
-      <c r="S8" s="125"/>
-      <c r="T8" s="125"/>
-      <c r="U8" s="126"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="121" t="s">
+      <c r="D8" s="98"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="99"/>
+      <c r="U8" s="100"/>
+    </row>
+    <row r="9" spans="1:21" ht="13.15">
+      <c r="A9" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="122"/>
-      <c r="C9" s="123" t="s">
+      <c r="B9" s="96"/>
+      <c r="C9" s="97" t="s">
         <v>534</v>
       </c>
-      <c r="D9" s="124"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="125"/>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
-      <c r="P9" s="125"/>
-      <c r="Q9" s="125"/>
-      <c r="R9" s="125"/>
-      <c r="S9" s="125"/>
-      <c r="T9" s="125"/>
-      <c r="U9" s="126"/>
-    </row>
-    <row r="10" spans="1:21" ht="13.8" thickBot="1">
-      <c r="A10" s="127" t="s">
+      <c r="D9" s="98"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="100"/>
+    </row>
+    <row r="10" spans="1:21" ht="13.5" thickBot="1">
+      <c r="A10" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="128"/>
-      <c r="C10" s="129" t="s">
+      <c r="B10" s="102"/>
+      <c r="C10" s="103" t="s">
         <v>535</v>
       </c>
-      <c r="D10" s="130"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="132"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="105"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="105"/>
+      <c r="S10" s="105"/>
+      <c r="T10" s="105"/>
+      <c r="U10" s="106"/>
     </row>
     <row r="11" spans="1:21" ht="9" customHeight="1" thickBot="1">
       <c r="A11" s="30"/>
       <c r="B11" s="42"/>
     </row>
-    <row r="12" spans="1:21" ht="14.4" thickBot="1">
-      <c r="A12" s="136" t="s">
+    <row r="12" spans="1:21" ht="13.9" thickBot="1">
+      <c r="A12" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="137"/>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="137"/>
-      <c r="K12" s="137"/>
-      <c r="L12" s="137"/>
-      <c r="M12" s="137"/>
-      <c r="N12" s="137"/>
-      <c r="O12" s="137"/>
-      <c r="P12" s="137"/>
-      <c r="Q12" s="137"/>
-      <c r="R12" s="137"/>
-      <c r="S12" s="137"/>
-      <c r="T12" s="137"/>
-      <c r="U12" s="138"/>
-    </row>
-    <row r="13" spans="1:21" ht="10.199999999999999" customHeight="1" thickBot="1">
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="112"/>
+    </row>
+    <row r="13" spans="1:21" ht="10.25" customHeight="1" thickBot="1">
       <c r="C13" s="31"/>
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
@@ -9160,7 +9163,7 @@
       <c r="S13" s="31"/>
       <c r="T13" s="31"/>
     </row>
-    <row r="14" spans="1:21" ht="26.4" customHeight="1" thickBot="1">
+    <row r="14" spans="1:21" ht="26.45" customHeight="1" thickBot="1">
       <c r="A14" s="43" t="s">
         <v>75</v>
       </c>
@@ -9173,23 +9176,23 @@
       <c r="D14" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="133" t="s">
+      <c r="E14" s="107" t="s">
         <v>78</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="133"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
-      <c r="N14" s="134"/>
-      <c r="O14" s="134"/>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="135"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="108"/>
+      <c r="S14" s="109"/>
       <c r="T14" s="44" t="s">
         <v>79</v>
       </c>
@@ -9224,7 +9227,7 @@
       <c r="T15" s="71"/>
       <c r="U15" s="58"/>
     </row>
-    <row r="16" spans="1:21" ht="13.8" thickBot="1">
+    <row r="16" spans="1:21" ht="13.15" thickBot="1">
       <c r="A16" s="92">
         <v>1.3888888888888889E-3</v>
       </c>
@@ -9319,7 +9322,7 @@
         <v>523</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>158</v>
+        <v>541</v>
       </c>
       <c r="F17" s="66" t="s">
         <v>446</v>
@@ -9342,7 +9345,7 @@
       </c>
       <c r="U17" s="88"/>
     </row>
-    <row r="18" spans="1:21" ht="13.8" thickBot="1">
+    <row r="18" spans="1:21" ht="13.15" thickBot="1">
       <c r="A18" s="94">
         <v>2.0833333333333333E-3</v>
       </c>
@@ -9457,7 +9460,7 @@
       <c r="T19" s="71"/>
       <c r="U19" s="58"/>
     </row>
-    <row r="20" spans="1:21" ht="13.8" thickBot="1">
+    <row r="20" spans="1:21" ht="13.15" thickBot="1">
       <c r="A20" s="94">
         <v>2.7777777777777779E-3</v>
       </c>
@@ -9574,7 +9577,7 @@
       <c r="T21" s="71"/>
       <c r="U21" s="58"/>
     </row>
-    <row r="22" spans="1:21" ht="13.8" thickBot="1">
+    <row r="22" spans="1:21" ht="13.15" thickBot="1">
       <c r="A22" s="94">
         <v>3.472222222222222E-3</v>
       </c>
@@ -9682,7 +9685,7 @@
       <c r="T23" s="71"/>
       <c r="U23" s="58"/>
     </row>
-    <row r="24" spans="1:21" ht="13.8" thickBot="1">
+    <row r="24" spans="1:21" ht="13.15" thickBot="1">
       <c r="A24" s="68"/>
       <c r="B24" s="46" t="s">
         <v>14</v>
@@ -9789,7 +9792,7 @@
       <c r="T25" s="71"/>
       <c r="U25" s="58"/>
     </row>
-    <row r="26" spans="1:21" ht="13.8" thickBot="1">
+    <row r="26" spans="1:21" ht="13.15" thickBot="1">
       <c r="A26" s="68"/>
       <c r="B26" s="46" t="s">
         <v>14</v>
@@ -9896,7 +9899,7 @@
       <c r="T27" s="71"/>
       <c r="U27" s="58"/>
     </row>
-    <row r="28" spans="1:21" ht="13.8" thickBot="1">
+    <row r="28" spans="1:21" ht="13.15" thickBot="1">
       <c r="A28" s="68"/>
       <c r="B28" s="46" t="s">
         <v>14</v>
@@ -10003,7 +10006,7 @@
       <c r="T29" s="71"/>
       <c r="U29" s="58"/>
     </row>
-    <row r="30" spans="1:21" ht="13.8" thickBot="1">
+    <row r="30" spans="1:21" ht="13.15" thickBot="1">
       <c r="A30" s="68"/>
       <c r="B30" s="46" t="s">
         <v>14</v>
@@ -10110,7 +10113,7 @@
       <c r="T31" s="71"/>
       <c r="U31" s="58"/>
     </row>
-    <row r="32" spans="1:21" ht="13.8" thickBot="1">
+    <row r="32" spans="1:21" ht="13.15" thickBot="1">
       <c r="A32" s="68"/>
       <c r="B32" s="46" t="s">
         <v>14</v>
@@ -10217,7 +10220,7 @@
       <c r="T33" s="71"/>
       <c r="U33" s="58"/>
     </row>
-    <row r="34" spans="1:21" ht="13.8" thickBot="1">
+    <row r="34" spans="1:21" ht="13.15" thickBot="1">
       <c r="A34" s="68"/>
       <c r="B34" s="46" t="s">
         <v>14</v>
@@ -10324,7 +10327,7 @@
       <c r="T35" s="71"/>
       <c r="U35" s="58"/>
     </row>
-    <row r="36" spans="1:21" ht="13.8" thickBot="1">
+    <row r="36" spans="1:21" ht="13.15" thickBot="1">
       <c r="A36" s="68"/>
       <c r="B36" s="46" t="s">
         <v>14</v>
@@ -10431,7 +10434,7 @@
       <c r="T37" s="71"/>
       <c r="U37" s="58"/>
     </row>
-    <row r="38" spans="1:21" ht="13.8" thickBot="1">
+    <row r="38" spans="1:21" ht="13.15" thickBot="1">
       <c r="A38" s="68"/>
       <c r="B38" s="46" t="s">
         <v>14</v>
@@ -10538,7 +10541,7 @@
       <c r="T39" s="71"/>
       <c r="U39" s="58"/>
     </row>
-    <row r="40" spans="1:21" ht="13.8" thickBot="1">
+    <row r="40" spans="1:21" ht="13.15" thickBot="1">
       <c r="A40" s="68"/>
       <c r="B40" s="46" t="s">
         <v>14</v>
@@ -10645,7 +10648,7 @@
       <c r="T41" s="71"/>
       <c r="U41" s="58"/>
     </row>
-    <row r="42" spans="1:21" ht="13.8" thickBot="1">
+    <row r="42" spans="1:21" ht="13.15" thickBot="1">
       <c r="A42" s="68"/>
       <c r="B42" s="46" t="s">
         <v>14</v>
@@ -10752,7 +10755,7 @@
       <c r="T43" s="71"/>
       <c r="U43" s="58"/>
     </row>
-    <row r="44" spans="1:21" ht="13.8" thickBot="1">
+    <row r="44" spans="1:21" ht="13.15" thickBot="1">
       <c r="A44" s="68"/>
       <c r="B44" s="46" t="s">
         <v>14</v>
@@ -10859,7 +10862,7 @@
       <c r="T45" s="71"/>
       <c r="U45" s="58"/>
     </row>
-    <row r="46" spans="1:21" ht="13.8" thickBot="1">
+    <row r="46" spans="1:21" ht="13.15" thickBot="1">
       <c r="A46" s="68"/>
       <c r="B46" s="46" t="s">
         <v>14</v>
@@ -10966,7 +10969,7 @@
       <c r="T47" s="71"/>
       <c r="U47" s="58"/>
     </row>
-    <row r="48" spans="1:21" ht="13.8" thickBot="1">
+    <row r="48" spans="1:21" ht="13.15" thickBot="1">
       <c r="A48" s="68"/>
       <c r="B48" s="46" t="s">
         <v>14</v>
@@ -11073,7 +11076,7 @@
       <c r="T49" s="71"/>
       <c r="U49" s="58"/>
     </row>
-    <row r="50" spans="1:21" ht="13.8" thickBot="1">
+    <row r="50" spans="1:21" ht="13.15" thickBot="1">
       <c r="A50" s="68"/>
       <c r="B50" s="46" t="s">
         <v>14</v>
@@ -11180,7 +11183,7 @@
       <c r="T51" s="71"/>
       <c r="U51" s="58"/>
     </row>
-    <row r="52" spans="1:21" ht="13.8" thickBot="1">
+    <row r="52" spans="1:21" ht="13.15" thickBot="1">
       <c r="A52" s="68"/>
       <c r="B52" s="46" t="s">
         <v>14</v>
@@ -11287,7 +11290,7 @@
       <c r="T53" s="71"/>
       <c r="U53" s="58"/>
     </row>
-    <row r="54" spans="1:21" ht="13.8" thickBot="1">
+    <row r="54" spans="1:21" ht="13.15" thickBot="1">
       <c r="A54" s="68"/>
       <c r="B54" s="46" t="s">
         <v>14</v>
@@ -11394,7 +11397,7 @@
       <c r="T55" s="71"/>
       <c r="U55" s="58"/>
     </row>
-    <row r="56" spans="1:21" ht="13.8" thickBot="1">
+    <row r="56" spans="1:21" ht="13.15" thickBot="1">
       <c r="A56" s="68"/>
       <c r="B56" s="46" t="s">
         <v>14</v>
@@ -11501,7 +11504,7 @@
       <c r="T57" s="71"/>
       <c r="U57" s="58"/>
     </row>
-    <row r="58" spans="1:21" ht="13.8" thickBot="1">
+    <row r="58" spans="1:21" ht="13.15" thickBot="1">
       <c r="A58" s="68"/>
       <c r="B58" s="46" t="s">
         <v>14</v>
@@ -11608,7 +11611,7 @@
       <c r="T59" s="71"/>
       <c r="U59" s="58"/>
     </row>
-    <row r="60" spans="1:21" ht="13.8" thickBot="1">
+    <row r="60" spans="1:21" ht="13.15" thickBot="1">
       <c r="A60" s="68"/>
       <c r="B60" s="46" t="s">
         <v>14</v>
@@ -11715,7 +11718,7 @@
       <c r="T61" s="71"/>
       <c r="U61" s="58"/>
     </row>
-    <row r="62" spans="1:21" ht="13.8" thickBot="1">
+    <row r="62" spans="1:21" ht="13.15" thickBot="1">
       <c r="A62" s="68"/>
       <c r="B62" s="46" t="s">
         <v>14</v>
@@ -11822,7 +11825,7 @@
       <c r="T63" s="71"/>
       <c r="U63" s="58"/>
     </row>
-    <row r="64" spans="1:21" ht="13.8" thickBot="1">
+    <row r="64" spans="1:21" ht="13.15" thickBot="1">
       <c r="A64" s="68"/>
       <c r="B64" s="46" t="s">
         <v>14</v>
@@ -11904,7 +11907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="20.399999999999999" customHeight="1" thickBot="1">
+    <row r="65" spans="1:21" ht="20.45" customHeight="1" thickBot="1">
       <c r="A65" s="47"/>
       <c r="B65" s="48"/>
       <c r="C65" s="48"/>
@@ -11932,18 +11935,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:U6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:U7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:U8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:U9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:U10"/>
     <mergeCell ref="E14:S14"/>
     <mergeCell ref="A12:U12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:U6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:U7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:U8"/>
   </mergeCells>
   <conditionalFormatting sqref="A7:A13">
     <cfRule type="containsText" dxfId="124" priority="141" operator="containsText" text=" ">
